--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>46053</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>45257</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45596</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>46275</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>46164</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45894</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45799</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>46274</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>46050</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>46184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46262</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>46211</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>45028</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44852</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45939</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45968</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>46167</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46170</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>46275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45394</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45446</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45926</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>46064</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45925</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45890</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44553</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>46274</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>46276</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>46282</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44705</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45120</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>46045</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>46064</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45202</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45747</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45846</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45733</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>45236</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45334</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>46258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>46248</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45789</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44538</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44538</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45564</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45902</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46049</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>46055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45945</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45600</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45356</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45945</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45243</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45971</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45096</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45992</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45989</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44525</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45831</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45114</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46164</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>46175</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45450</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44525</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>46191</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45625</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>46206</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>46210</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45439</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>46262</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>46266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>46220</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>46272</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>46276</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46280</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46283</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45119</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44636</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45768</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45987</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>46184</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44866</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44536</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44531</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44817</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44538</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44498</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>44857</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>44777</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44495</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44816</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44848</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44582</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44599</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44481</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44502</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44543</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44592</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44708</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44816</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44811</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44499</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44817</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44496</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44818</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>44616</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44820</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44503</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44816</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44886</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44590</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44538</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44480</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44735</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44571</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45681</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45177</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45705</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45334</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45257</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45350</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45419</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45356</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45363</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44817</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>44813</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45254</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44824</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45478</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45478</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45457</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45264</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45418</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45230</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45936</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45237</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45938</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45936</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45936</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45936</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45586</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45377</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45117</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45219</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45313</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44950</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44538</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45266</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45035</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45505</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45478</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45544</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45180</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45488</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45764</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>46036</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45532</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>46036</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45511</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45769</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46038</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45559</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45559</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45610</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45894</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45891</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45467</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45635</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46042</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46042</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>46042</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46042</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>46042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>46038</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46042</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>46044</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>46043</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45897</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>44592</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45897</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>46048</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45379</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46045</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45880</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45545</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45903</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45618</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>46049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>46050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>44608</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45800</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45905</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>46051</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45491</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45912</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44942</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>46057</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>46058</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45915</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45741</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>46068</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45120</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45120</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45578</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45347</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45924</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45015</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45926</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45565</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45925</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45553</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45925</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45531</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45929</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45929</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45929</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45929</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45145</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45929</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>46080</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>46083</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45264</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>44531</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45807</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45028</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45935</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>46087</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>46087</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45935</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45541</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45285</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45419</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45935</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45585</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44622</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46092</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45940</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45940</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45244</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45548</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45940</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45944</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>44977</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45783</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45945</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45945</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45950</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44782</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45553</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45951</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45952</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45741</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45741</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>44941</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45953</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45955</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45955</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45955</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45955</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45956</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44756</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45960</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45960</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45960</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45959</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45568</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45574</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45964</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45098</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45323</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>46122</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>46126</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45968</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45971</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45971</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45971</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>44722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45644</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45974</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45642</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45642</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45978</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45975</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45980</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44929</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>44929</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44911</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44907</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45981</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45982</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45982</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>45981</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45981</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45695</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45985</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45985</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>46135</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45986</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45985</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45985</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45553</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45681</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>46136</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>46135</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45988</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>46135</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>45701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44859</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45989</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45993</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45842</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45898</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45993</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45742</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45741</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>45995</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45995</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45183</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45641</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45021</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45776</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45375</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45924</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45952</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45936</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45323</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>46002</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>45098</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44890</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>45985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45958</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45972</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45664</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>46002</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>46006</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>46006</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45188</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45862</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>46006</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>46006</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46006</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>46006</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46006</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>46006</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46006</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45677</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45946</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45685</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45936</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45820</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46008</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45760</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45849</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46008</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46034</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45478</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45926</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45924</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45714</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>46010</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45827</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45833</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46010</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45894</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45926</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45926</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45930</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45797</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>46013</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45908</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45848</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45824</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45370</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45901</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45819</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45478</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>44895</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45670</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45965</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45526</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45904</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45684</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45890</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45937</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46140</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45942</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45911</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>46142</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45934</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45825</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45688</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45265</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45827</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45523</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45180</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42585,7 +42585,7 @@
         <v>45772</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45832</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>45262</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44468</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45345</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>46150</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>44972</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>46150</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>46150</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>45700</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>46150</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45167</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>46153</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>46154</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45225</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45834</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45558</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45912</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45376</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>44890</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45090</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46161</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45285</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45312</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45110</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45987</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46162</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>46161</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>45188</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46162</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45350</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45582</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45955</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45881</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45245</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45848</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>44685</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45848</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45849</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>44550</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45400</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45700</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45363</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45376</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>46168</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45574</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45574</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46168</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45139</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>45247</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45828</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45573</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45799</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44741</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44879</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44879</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>44741</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45229</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>44516</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>44523</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>44588</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>44687</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>44775</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>44623</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44596</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45467</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>44529</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46171</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45769</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45376</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>45324</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45544</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46175</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>46177</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>46177</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>46177</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>46177</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>46177</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>46177</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45627</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>46036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>45202</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>45442</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45273</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45747</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>46178</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45239</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46183</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>46183</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45873</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>46183</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>46183</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45503</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45874</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45401</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>46188</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45874</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45527</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45527</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>46190</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45576</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44806</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46195</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46197</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>46197</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45877</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45880</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45880</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45420</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>45559</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45596</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>45478</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50906,7 +50906,7 @@
         <v>45208</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>46203</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51052,7 +51052,7 @@
         <v>45187</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45644</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45230</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>46203</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>45601</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>46203</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45056</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45056</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>45043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>46205</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45605</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>45345</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45883</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>46205</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>45684</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>46252</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>44658</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>46252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>46251</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>46252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>46206</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52688,7 +52688,7 @@
         <v>46251</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45097</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52839,7 +52839,7 @@
         <v>44685</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>46252</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45090</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45687</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45600</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>46254</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45188</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>46211</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>45239</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>46197</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>46210</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>46210</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>46254</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>45706</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45238</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>46254</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>46254</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45138</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>44656</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>46258</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46258</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>46255</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>46212</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46212</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>46212</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>46212</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>46212</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>45642</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>46260</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45098</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46217</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>46217</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45243</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55333,7 +55333,7 @@
         <v>45243</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>46206</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55484,7 +55484,7 @@
         <v>45177</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>44683</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55630,7 +55630,7 @@
         <v>46217</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>46261</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55786,7 +55786,7 @@
         <v>46262</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>45215</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>46262</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>46191</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>46262</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>46223</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>44792</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45129</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45414</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>45215</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>46266</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>46266</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56672,7 +56672,7 @@
         <v>46266</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>46191</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>46266</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>45244</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>45245</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>46223</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45987</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>46223</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>46223</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>45167</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>46111</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45320</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>46223</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45974</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>46265</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>46265</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57865,7 +57865,7 @@
         <v>46266</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>46268</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46268</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>46267</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>46267</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46265</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45219</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>46272</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58464,7 +58464,7 @@
         <v>46226</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>45251</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58615,7 +58615,7 @@
         <v>46268</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58693,7 +58693,7 @@
         <v>46268</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>46268</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>46126</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45287</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46272</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>46272</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46268</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46226</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>46272</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>46272</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59531,7 +59531,7 @@
         <v>46273</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>46230</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45265</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>46274</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45749</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46276</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>44785</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60057,7 +60057,7 @@
         <v>45484</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46275</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>45324</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>44685</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>46237</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45187</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>46237</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>46237</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46237</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>46280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60880,7 +60880,7 @@
         <v>46237</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60953,7 +60953,7 @@
         <v>45273</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>46280</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45484</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>45393</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>46230</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>46238</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>44874</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61479,7 +61479,7 @@
         <v>44984</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>46230</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>45579</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45579</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>45601</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>44971</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61917,7 +61917,7 @@
         <v>45552</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>46230</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62063,7 +62063,7 @@
         <v>46230</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>45646</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62209,7 +62209,7 @@
         <v>45678</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62282,7 +62282,7 @@
         <v>46283</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62360,7 +62360,7 @@
         <v>46285</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>46154</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62506,7 +62506,7 @@
         <v>45646</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>46286</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45559</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62730,7 +62730,7 @@
         <v>44525</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>45546</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>46275</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>46275</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>46281</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63178,7 +63178,7 @@
         <v>46286</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63256,7 +63256,7 @@
         <v>46245</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>46245</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>45981</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63475,7 +63475,7 @@
         <v>46245</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63548,7 +63548,7 @@
         <v>46245</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>46244</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>46288</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>46244</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>46245</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>46244</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63996,7 +63996,7 @@
         <v>46267</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>46287</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64147,7 +64147,7 @@
         <v>46244</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64220,7 +64220,7 @@
         <v>46247</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64293,7 +64293,7 @@
         <v>45419</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64366,7 +64366,7 @@
         <v>44615</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>45642</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>46290</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45604</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>46247</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>46247</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>45316</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64882,7 +64882,7 @@
         <v>45176</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>46247</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65028,7 +65028,7 @@
         <v>46248</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65106,7 +65106,7 @@
         <v>45425</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45603</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45596</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45593</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>44917</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45106</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45245</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>44942</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>44708</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>44538</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>45211</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45097</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>45254</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45232</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66143,7 +66143,7 @@
         <v>45350</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45607</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>45308</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45309</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66435,7 +66435,7 @@
         <v>45617</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45537</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>45586</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>45620</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>45523</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66810,7 +66810,7 @@
         <v>44813</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>44984</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         <v>45271</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67029,7 +67029,7 @@
         <v>45434</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>44942</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67175,7 +67175,7 @@
         <v>45222</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>45726</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>44708</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67394,7 +67394,7 @@
         <v>45167</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67472,7 +67472,7 @@
         <v>45625</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>44874</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>45237</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67691,7 +67691,7 @@
         <v>45579</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>45579</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67837,7 +67837,7 @@
         <v>45140</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67915,7 +67915,7 @@
         <v>45331</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67988,7 +67988,7 @@
         <v>45478</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68061,7 +68061,7 @@
         <v>45440</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68134,7 +68134,7 @@
         <v>45618</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>45559</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68280,7 +68280,7 @@
         <v>45278</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>45462</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68426,7 +68426,7 @@
         <v>45573</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68499,7 +68499,7 @@
         <v>45281</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68572,7 +68572,7 @@
         <v>45631</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68645,7 +68645,7 @@
         <v>45434</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68718,7 +68718,7 @@
         <v>45273</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68791,7 +68791,7 @@
         <v>45125</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68864,7 +68864,7 @@
         <v>45125</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68937,7 +68937,7 @@
         <v>45574</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69015,7 +69015,7 @@
         <v>45574</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69093,7 +69093,7 @@
         <v>45639</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69166,7 +69166,7 @@
         <v>45776</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69239,7 +69239,7 @@
         <v>45357</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69312,7 +69312,7 @@
         <v>45405</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>45434</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69458,7 +69458,7 @@
         <v>45782</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69531,7 +69531,7 @@
         <v>45782</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69604,7 +69604,7 @@
         <v>45783</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>45315</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69755,7 +69755,7 @@
         <v>45315</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69828,7 +69828,7 @@
         <v>45090</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>45110</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         <v>45701</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70047,7 +70047,7 @@
         <v>45462</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70120,7 +70120,7 @@
         <v>45141</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70193,7 +70193,7 @@
         <v>45791</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70266,7 +70266,7 @@
         <v>44795</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70339,7 +70339,7 @@
         <v>45476</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70412,7 +70412,7 @@
         <v>45113</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70490,7 +70490,7 @@
         <v>45013</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70568,7 +70568,7 @@
         <v>45114</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>45440</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70714,7 +70714,7 @@
         <v>44825</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70787,7 +70787,7 @@
         <v>45070</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70860,7 +70860,7 @@
         <v>44741</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70938,7 +70938,7 @@
         <v>45688</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71011,7 +71011,7 @@
         <v>45743</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71084,7 +71084,7 @@
         <v>45743</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71157,7 +71157,7 @@
         <v>45743</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71230,7 +71230,7 @@
         <v>45743</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71303,7 +71303,7 @@
         <v>46127</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71376,7 +71376,7 @@
         <v>46147</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>46053</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>45257</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45596</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>46275</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>46164</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45894</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45799</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>46274</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>46050</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>46184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46262</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>46211</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>45028</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44852</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45939</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45968</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>46167</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46170</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>46275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45394</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45446</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45926</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>46064</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45925</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45890</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44553</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>46274</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>46276</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>46282</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44705</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45120</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>46045</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>46064</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45202</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45747</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45846</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45733</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>45236</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45334</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>46258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>46248</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45789</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44538</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44538</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45564</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45902</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46049</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>46055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45945</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45600</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45356</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45945</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45243</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45971</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45096</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45992</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45989</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44525</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45831</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45114</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46164</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>46175</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45450</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44525</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>46191</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45625</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>46206</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>46210</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45439</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>46262</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>46266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>46220</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>46272</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>46276</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46280</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46283</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45119</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44636</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45768</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45987</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>46184</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44866</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44536</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44531</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44817</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44538</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44498</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>44857</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>44777</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44495</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44816</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44848</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44582</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44599</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44481</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44502</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44543</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44592</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44708</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44816</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44811</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44499</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44817</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44496</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44818</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>44616</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44820</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44503</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44816</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44886</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44590</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44538</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44480</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44735</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44571</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45681</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45177</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45705</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45334</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45257</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45350</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45419</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45356</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45363</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44817</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>44813</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45254</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44824</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45478</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45478</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45457</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45264</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45418</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45230</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45936</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45237</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45938</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45936</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45936</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45936</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45586</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45377</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45117</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45219</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45313</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44950</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44538</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45266</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45035</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45505</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45478</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45544</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45180</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45488</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45764</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>46036</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45532</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>46036</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45511</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45769</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46038</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45559</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45559</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45610</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45894</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45891</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45467</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45635</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46042</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46042</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>46042</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46042</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>46042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>46038</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46042</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>46044</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>46043</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45897</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>44592</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45897</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>46048</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45379</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46045</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45880</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45545</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45903</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45618</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>46049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>46050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>44608</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45800</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45905</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>46051</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45491</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45912</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44942</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>46057</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>46058</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45915</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45741</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>46068</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45120</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45120</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45578</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45347</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45924</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45015</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45926</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45565</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45925</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45553</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45925</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45531</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45929</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45929</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45929</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45929</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45145</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45929</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>46080</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>46083</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45264</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>44531</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45807</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45028</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45935</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>46087</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>46087</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45935</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45541</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45285</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45419</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45935</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45585</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44622</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46092</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45940</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45940</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45244</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45548</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45940</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45944</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>44977</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45783</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45945</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45945</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45950</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44782</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45553</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45951</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45952</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45741</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45741</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>44941</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45953</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45955</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45955</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45955</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45955</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45956</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44756</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45960</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45960</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45960</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45959</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45568</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45574</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45964</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45098</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45323</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>46122</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>46126</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45968</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45971</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45971</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45971</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>44722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45644</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45974</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45642</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45642</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45978</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45975</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45980</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44929</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>44929</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44911</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44907</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45981</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45982</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45982</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>45981</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45981</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45695</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45985</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45985</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>46135</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45986</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45985</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45985</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45553</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45681</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>46136</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>46135</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45988</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>46135</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>45701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44859</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45989</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45993</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45842</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45898</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45993</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45742</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45741</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>45995</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45995</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45183</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45641</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45021</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45776</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45375</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45924</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45952</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45936</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45323</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>46002</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>45098</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44890</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>45985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45958</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45972</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45664</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>46002</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>46006</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>46006</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45188</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45862</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>46006</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>46006</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46006</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>46006</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46006</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>46006</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46006</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45677</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45946</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45685</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45936</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45820</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46008</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45760</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45849</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46008</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46034</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45478</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45926</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45924</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45714</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>46010</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45827</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45833</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46010</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45894</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45926</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45926</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45930</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45797</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>46013</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45908</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45848</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45824</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45370</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45901</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45819</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45478</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>44895</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45670</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45965</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45526</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45904</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45684</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45890</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45937</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46140</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45942</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45911</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>46142</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45934</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45825</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45688</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45265</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45827</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45523</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45180</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42585,7 +42585,7 @@
         <v>45772</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45832</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>45262</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44468</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45345</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>46150</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>44972</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>46150</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>46150</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>45700</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>46150</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45167</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>46153</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>46154</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45225</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45834</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45558</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45912</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45376</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>44890</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45090</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46161</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45285</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45312</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45110</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45987</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46162</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>46161</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>45188</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46162</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45350</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45582</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45955</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45881</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45245</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45848</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>44685</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45848</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45849</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>44550</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45400</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45700</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45363</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45376</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>46168</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45574</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45574</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46168</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45139</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>45247</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45828</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45573</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45799</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44741</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44879</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44879</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>44741</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45229</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>44516</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>44523</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>44588</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>44687</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>44775</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>44623</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44596</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45467</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>44529</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46171</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45769</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45376</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>45324</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45544</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46175</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>46177</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>46177</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>46177</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>46177</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>46177</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>46177</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45627</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>46036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>45202</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>45442</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45273</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45747</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>46178</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45239</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46183</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>46183</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45873</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>46183</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>46183</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45503</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45874</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45401</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>46188</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45874</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45527</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45527</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>46190</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45576</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44806</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46195</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46197</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>46197</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45877</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45880</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45880</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45420</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>45559</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45596</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>45478</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50906,7 +50906,7 @@
         <v>45208</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>46203</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51052,7 +51052,7 @@
         <v>45187</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45644</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45230</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>46203</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>45601</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>46203</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45056</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45056</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>45043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>46205</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45605</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>45345</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45883</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>46205</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>45684</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>46252</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>44658</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>46252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>46251</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>46252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>46206</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52688,7 +52688,7 @@
         <v>46251</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45097</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52839,7 +52839,7 @@
         <v>44685</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>46252</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45090</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45687</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45600</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>46254</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45188</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>46211</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>45239</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>46197</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>46210</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>46210</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>46254</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>45706</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45238</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>46254</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>46254</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>45138</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>44656</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>46258</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46258</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>46255</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>46212</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46212</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>46212</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>46212</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>46212</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>45642</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>46260</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45098</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46217</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>46217</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45243</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55333,7 +55333,7 @@
         <v>45243</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>46206</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55484,7 +55484,7 @@
         <v>45177</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>44683</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55630,7 +55630,7 @@
         <v>46217</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>46261</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55786,7 +55786,7 @@
         <v>46262</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>45215</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>46262</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>46191</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>46262</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>46223</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>44792</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45129</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45414</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>45215</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>46266</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>46266</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56672,7 +56672,7 @@
         <v>46266</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>46191</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>46266</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>45244</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>45245</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>46223</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45987</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>46223</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>46223</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>45167</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>46111</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45320</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>46223</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45974</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>46265</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>46265</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57865,7 +57865,7 @@
         <v>46266</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>46268</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46268</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>46267</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>46267</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46265</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45219</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>46272</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58464,7 +58464,7 @@
         <v>46226</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>45251</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58615,7 +58615,7 @@
         <v>46268</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58693,7 +58693,7 @@
         <v>46268</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>46268</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>46126</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45287</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46272</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>46272</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46268</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46226</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>46272</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>46272</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59531,7 +59531,7 @@
         <v>46273</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>46230</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45265</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>46274</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45749</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46276</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>44785</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60057,7 +60057,7 @@
         <v>45484</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46275</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>45324</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>44685</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>46237</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45187</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>46237</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>46237</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46237</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>46280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60880,7 +60880,7 @@
         <v>46237</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60953,7 +60953,7 @@
         <v>45273</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>46280</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45484</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>45393</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>46230</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>46238</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>44874</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61479,7 +61479,7 @@
         <v>44984</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>46230</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>45579</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45579</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>45601</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>44971</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61917,7 +61917,7 @@
         <v>45552</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>46230</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62063,7 +62063,7 @@
         <v>46230</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>45646</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62209,7 +62209,7 @@
         <v>45678</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62282,7 +62282,7 @@
         <v>46283</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62360,7 +62360,7 @@
         <v>46285</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>46154</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62506,7 +62506,7 @@
         <v>45646</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>46286</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45559</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62730,7 +62730,7 @@
         <v>44525</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>45546</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>46275</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>46275</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>46281</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63178,7 +63178,7 @@
         <v>46286</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63256,7 +63256,7 @@
         <v>46245</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>46245</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>45981</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63475,7 +63475,7 @@
         <v>46245</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63548,7 +63548,7 @@
         <v>46245</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>46244</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>46288</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>46244</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>46245</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>46244</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63996,7 +63996,7 @@
         <v>46267</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>46287</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64147,7 +64147,7 @@
         <v>46244</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64220,7 +64220,7 @@
         <v>46247</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64293,7 +64293,7 @@
         <v>45419</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64366,7 +64366,7 @@
         <v>44615</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>45642</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>46290</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45604</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>46247</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>46247</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>45316</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64882,7 +64882,7 @@
         <v>45176</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>46247</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65028,7 +65028,7 @@
         <v>46248</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65106,7 +65106,7 @@
         <v>45425</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45603</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45596</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45593</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>44917</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45106</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45245</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>44942</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>44708</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>44538</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>45211</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45097</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>45254</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45232</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66143,7 +66143,7 @@
         <v>45350</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45607</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>45308</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45309</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66435,7 +66435,7 @@
         <v>45617</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45537</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>45586</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>45620</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>45523</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66810,7 +66810,7 @@
         <v>44813</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>44984</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         <v>45271</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67029,7 +67029,7 @@
         <v>45434</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>44942</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67175,7 +67175,7 @@
         <v>45222</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>45726</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>44708</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67394,7 +67394,7 @@
         <v>45167</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67472,7 +67472,7 @@
         <v>45625</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>44874</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>45237</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67691,7 +67691,7 @@
         <v>45579</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>45579</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67837,7 +67837,7 @@
         <v>45140</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67915,7 +67915,7 @@
         <v>45331</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67988,7 +67988,7 @@
         <v>45478</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68061,7 +68061,7 @@
         <v>45440</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68134,7 +68134,7 @@
         <v>45618</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>45559</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68280,7 +68280,7 @@
         <v>45278</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>45462</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68426,7 +68426,7 @@
         <v>45573</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68499,7 +68499,7 @@
         <v>45281</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68572,7 +68572,7 @@
         <v>45631</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68645,7 +68645,7 @@
         <v>45434</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68718,7 +68718,7 @@
         <v>45273</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68791,7 +68791,7 @@
         <v>45125</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68864,7 +68864,7 @@
         <v>45125</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68937,7 +68937,7 @@
         <v>45574</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69015,7 +69015,7 @@
         <v>45574</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69093,7 +69093,7 @@
         <v>45639</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69166,7 +69166,7 @@
         <v>45776</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69239,7 +69239,7 @@
         <v>45357</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69312,7 +69312,7 @@
         <v>45405</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>45434</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69458,7 +69458,7 @@
         <v>45782</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69531,7 +69531,7 @@
         <v>45782</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69604,7 +69604,7 @@
         <v>45783</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>45315</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69755,7 +69755,7 @@
         <v>45315</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69828,7 +69828,7 @@
         <v>45090</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>45110</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         <v>45701</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70047,7 +70047,7 @@
         <v>45462</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70120,7 +70120,7 @@
         <v>45141</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70193,7 +70193,7 @@
         <v>45791</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70266,7 +70266,7 @@
         <v>44795</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70339,7 +70339,7 @@
         <v>45476</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70412,7 +70412,7 @@
         <v>45113</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70490,7 +70490,7 @@
         <v>45013</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70568,7 +70568,7 @@
         <v>45114</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>45440</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70714,7 +70714,7 @@
         <v>44825</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70787,7 +70787,7 @@
         <v>45070</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70860,7 +70860,7 @@
         <v>44741</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70938,7 +70938,7 @@
         <v>45688</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71011,7 +71011,7 @@
         <v>45743</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71084,7 +71084,7 @@
         <v>45743</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71157,7 +71157,7 @@
         <v>45743</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71230,7 +71230,7 @@
         <v>45743</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71303,7 +71303,7 @@
         <v>46127</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71376,7 +71376,7 @@
         <v>46147</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>46053</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>46258</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>45257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45596</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>46006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45898</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>46167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45799</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46297</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46064</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46262</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45028</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44852</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46170</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45119</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45394</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44553</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45926</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46057</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44727</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45890</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46274</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>46276</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>46282</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45243</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45120</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45761</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>46045</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45922</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>46064</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45935</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45236</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45955</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45334</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45747</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45733</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46293</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>46248</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46296</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44582</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44538</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>46049</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>46055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45439</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45945</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45945</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45356</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45096</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45971</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45820</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45989</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45992</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45564</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45827</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45644</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>46164</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>46175</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>46183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>46191</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46206</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45114</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44525</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>46210</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45243</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46258</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46220</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46262</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>46266</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>46225</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>46272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>46276</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>46237</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45625</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46283</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45119</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45450</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45565</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45768</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45987</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>44866</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44536</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44538</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>44747</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44498</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>44857</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>44777</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44495</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44816</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>44582</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44599</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44481</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>44502</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44489</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44538</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44543</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>44592</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44742</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44816</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44811</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>44499</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>44708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>44817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44496</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44818</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44590</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44820</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44816</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44886</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44590</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44538</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44480</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>44735</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44700</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44571</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45601</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45440</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45478</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45532</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45532</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45265</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45747</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45684</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45363</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44984</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44941</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45363</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45548</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45670</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45511</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45418</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45600</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45350</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45350</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45523</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>44708</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45254</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45425</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44538</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45180</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>46002</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45264</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45414</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45576</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44895</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44806</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45208</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>46002</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>46006</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>46006</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46006</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46006</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46006</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45167</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>46006</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46006</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45377</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45930</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45544</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46008</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46008</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45926</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45926</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45356</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>46010</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>46013</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46010</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45926</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46013</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45938</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45936</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45769</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45586</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>45764</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45586</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45891</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44859</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45309</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45691</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45894</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45141</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45894</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46031</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45896</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45897</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45345</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45110</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45951</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44795</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45145</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46036</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>46036</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45880</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45376</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45905</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45219</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>46038</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45904</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>46038</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46043</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>46043</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44792</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>46042</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46042</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46042</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45219</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45313</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45631</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45230</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44538</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45911</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46045</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46044</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46044</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45912</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46048</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>46049</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45379</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45916</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45467</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>46050</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44592</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45800</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46051</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45644</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46051</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45215</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45347</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45807</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45553</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45090</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45922</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45257</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45925</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45925</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45924</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45262</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45924</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45681</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45924</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46057</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45183</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45929</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>44977</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45350</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45929</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45929</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45929</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45926</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46058</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45929</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45323</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45230</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45935</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45935</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45935</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45604</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46068</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45574</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45484</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45940</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45940</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45940</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44890</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45944</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45783</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45187</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>45945</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45585</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45324</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45945</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45946</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>44531</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45950</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>46080</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45951</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>44950</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45245</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45953</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46083</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>45952</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>45957</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45957</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>45955</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45956</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45642</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45955</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45955</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45952</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45955</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46087</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46087</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45097</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45568</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45959</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45503</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45960</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46092</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45960</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45043</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45559</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45964</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45287</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>44685</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45244</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45574</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45574</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44615</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45559</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45559</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45188</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45971</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45457</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45968</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45635</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44756</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45285</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45975</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45978</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45685</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45618</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45981</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45980</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45985</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45985</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45982</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45982</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46036</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45488</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45986</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45167</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45986</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45824</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45244</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45701</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45988</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45989</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>44722</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>46122</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45827</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45531</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45574</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45574</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44782</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45462</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45995</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45742</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45741</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45993</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45995</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45700</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45642</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>46135</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>46135</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45832</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>46135</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45678</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45834</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45467</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45937</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45247</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45225</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45819</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45936</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45239</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45904</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45098</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45641</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45833</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45848</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45323</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45898</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45849</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45946</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45664</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45848</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45684</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45523</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45848</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45849</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45862</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45714</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45376</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>45760</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>45831</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46136</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>45827</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>45098</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>45370</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45237</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45894</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45324</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45901</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45936</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45965</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45237</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>44874</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45908</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45799</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45393</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44685</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45376</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45828</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45573</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45924</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45334</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45180</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45375</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45664</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>44596</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44623</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44588</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44879</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45911</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>44824</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>44516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>44608</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45797</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44879</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44775</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>44741</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>44741</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45552</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44687</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44523</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45646</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45842</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>44917</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45972</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45642</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45345</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45769</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45890</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45553</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45934</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45419</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>45985</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45478</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45942</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45958</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45544</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45232</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>45021</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45271</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45573</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45924</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45631</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>46140</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45776</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45873</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>46142</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45642</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>44525</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45419</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>45139</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45442</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45625</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46150</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46150</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>46153</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45097</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>46150</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>46150</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45265</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>45596</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45106</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>45175</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45239</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>46154</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>46161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45874</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45874</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46161</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45912</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>44656</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>46162</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44550</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>46162</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45308</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45478</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45478</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45695</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45987</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45035</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45035</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>45881</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45955</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45620</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45400</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45700</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45188</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45877</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45478</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45705</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45880</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>46168</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>46168</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>45726</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45880</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45129</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45541</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>45278</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>46171</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>46177</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46177</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45618</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>45883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>46175</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>46177</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>46177</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>46036</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45644</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>46177</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>46178</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>46177</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45558</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>46183</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>46183</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>46183</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>46188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45434</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>46190</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45605</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45202</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45772</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>46197</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>46195</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>46197</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44529</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45215</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>45706</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>45741</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>44929</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>44929</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>45537</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45644</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45526</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>45601</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>46203</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>46203</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>46203</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45484</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>46203</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>46205</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53963,7 +53963,7 @@
         <v>45015</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>46206</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>46205</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45553</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>45285</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45243</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>46210</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45243</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>46210</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>44817</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>44817</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45434</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>46212</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46197</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55015,7 +55015,7 @@
         <v>46212</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>46212</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>46211</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>46212</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>46212</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>46206</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44539</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45582</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45120</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45120</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46258</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>46258</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55931,7 +55931,7 @@
         <v>45578</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>46217</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45546</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56160,7 +56160,7 @@
         <v>46217</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>44984</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>46260</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>46217</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>46191</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45681</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>46261</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>46111</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45974</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>46262</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56910,7 +56910,7 @@
         <v>46262</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         <v>46262</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57061,7 +57061,7 @@
         <v>45987</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45188</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>46191</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57305,7 +57305,7 @@
         <v>46265</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>46265</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57451,7 +57451,7 @@
         <v>46265</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>46266</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46266</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>46267</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57748,7 +57748,7 @@
         <v>46223</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>46223</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>46223</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>46223</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>46267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>45419</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>46223</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58264,7 +58264,7 @@
         <v>45545</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>46266</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>46266</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>46266</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46226</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45688</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>46268</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45579</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45579</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>45579</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59004,7 +59004,7 @@
         <v>45579</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>46226</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>46268</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>46268</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45222</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59379,7 +59379,7 @@
         <v>46272</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>44685</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>46126</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45505</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>46268</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46268</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46272</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46230</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>46272</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>46272</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>46272</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         <v>46268</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60295,7 +60295,7 @@
         <v>46272</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>46273</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>46274</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>46275</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>45749</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>46276</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>45630</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>46237</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46237</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>46280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>46237</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61201,7 +61201,7 @@
         <v>46237</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61274,7 +61274,7 @@
         <v>46230</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>46230</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>46280</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>46238</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46230</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>45239</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46237</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>44942</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46283</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>44813</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45677</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>46281</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62165,7 +62165,7 @@
         <v>46283</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62243,7 +62243,7 @@
         <v>46275</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62316,7 +62316,7 @@
         <v>45559</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62389,7 +62389,7 @@
         <v>46275</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62462,7 +62462,7 @@
         <v>46286</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>46286</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45593</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62691,7 +62691,7 @@
         <v>45117</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62769,7 +62769,7 @@
         <v>45981</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62842,7 +62842,7 @@
         <v>44890</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>46287</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62988,7 +62988,7 @@
         <v>46285</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45401</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>46244</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>45273</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46154</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63353,7 +63353,7 @@
         <v>46244</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>46244</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63509,7 +63509,7 @@
         <v>45187</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>46244</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>46267</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63733,7 +63733,7 @@
         <v>46245</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>46245</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63879,7 +63879,7 @@
         <v>45491</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63952,7 +63952,7 @@
         <v>46245</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>46245</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64098,7 +64098,7 @@
         <v>46288</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64171,7 +64171,7 @@
         <v>46245</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64244,7 +64244,7 @@
         <v>46248</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>46293</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64400,7 +64400,7 @@
         <v>45245</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>46293</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>45903</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>46247</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>46290</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>45527</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>45527</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64931,7 +64931,7 @@
         <v>46293</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>46247</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65077,7 +65077,7 @@
         <v>46247</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65150,7 +65150,7 @@
         <v>45098</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65223,7 +65223,7 @@
         <v>45639</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         <v>46247</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65369,7 +65369,7 @@
         <v>45239</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65442,7 +65442,7 @@
         <v>45559</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>45603</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65588,7 +65588,7 @@
         <v>46251</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65661,7 +65661,7 @@
         <v>46252</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>46252</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65885,7 +65885,7 @@
         <v>44785</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65958,7 +65958,7 @@
         <v>46294</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46252</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         <v>46294</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45211</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66255,7 +66255,7 @@
         <v>46297</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66328,7 +66328,7 @@
         <v>46297</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66401,7 +66401,7 @@
         <v>45167</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>45090</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66552,7 +66552,7 @@
         <v>46297</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66625,7 +66625,7 @@
         <v>45043</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66698,7 +66698,7 @@
         <v>45607</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66771,7 +66771,7 @@
         <v>46296</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66849,7 +66849,7 @@
         <v>46252</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66922,7 +66922,7 @@
         <v>46230</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66995,7 +66995,7 @@
         <v>45125</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67068,7 +67068,7 @@
         <v>45125</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67141,7 +67141,7 @@
         <v>46254</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67214,7 +67214,7 @@
         <v>44888</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67287,7 +67287,7 @@
         <v>45478</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67360,7 +67360,7 @@
         <v>45478</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67433,7 +67433,7 @@
         <v>44622</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>46296</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67579,7 +67579,7 @@
         <v>46255</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67652,7 +67652,7 @@
         <v>44942</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67725,7 +67725,7 @@
         <v>46254</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67803,7 +67803,7 @@
         <v>46297</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67876,7 +67876,7 @@
         <v>46297</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46254</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68032,7 +68032,7 @@
         <v>46254</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68105,7 +68105,7 @@
         <v>45420</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68178,7 +68178,7 @@
         <v>45610</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68256,7 +68256,7 @@
         <v>45140</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>45627</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>44658</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68480,7 +68480,7 @@
         <v>45176</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45273</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68626,7 +68626,7 @@
         <v>44874</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68704,7 +68704,7 @@
         <v>45238</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68777,7 +68777,7 @@
         <v>44971</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>44708</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68923,7 +68923,7 @@
         <v>45596</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69001,7 +69001,7 @@
         <v>45617</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69079,7 +69079,7 @@
         <v>44907</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69152,7 +69152,7 @@
         <v>45229</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69230,7 +69230,7 @@
         <v>45273</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69303,7 +69303,7 @@
         <v>45331</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69376,7 +69376,7 @@
         <v>45741</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69449,7 +69449,7 @@
         <v>45741</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69522,7 +69522,7 @@
         <v>45312</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69595,7 +69595,7 @@
         <v>45316</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69668,7 +69668,7 @@
         <v>45244</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69741,7 +69741,7 @@
         <v>45056</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69814,7 +69814,7 @@
         <v>45056</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69887,7 +69887,7 @@
         <v>44813</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69960,7 +69960,7 @@
         <v>45251</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70033,7 +70033,7 @@
         <v>45254</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70106,7 +70106,7 @@
         <v>45646</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70179,7 +70179,7 @@
         <v>44972</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70252,7 +70252,7 @@
         <v>45687</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70325,7 +70325,7 @@
         <v>44817</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70403,7 +70403,7 @@
         <v>45138</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70476,7 +70476,7 @@
         <v>45028</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70549,7 +70549,7 @@
         <v>45177</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70622,7 +70622,7 @@
         <v>45776</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70695,7 +70695,7 @@
         <v>45405</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45434</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70841,7 +70841,7 @@
         <v>45357</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70914,7 +70914,7 @@
         <v>45782</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70987,7 +70987,7 @@
         <v>45782</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71060,7 +71060,7 @@
         <v>45783</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71138,7 +71138,7 @@
         <v>45090</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71211,7 +71211,7 @@
         <v>45462</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71284,7 +71284,7 @@
         <v>45110</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71357,7 +71357,7 @@
         <v>45315</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71430,7 +71430,7 @@
         <v>45315</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71503,7 +71503,7 @@
         <v>45476</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71576,7 +71576,7 @@
         <v>45113</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71654,7 +71654,7 @@
         <v>45013</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71732,7 +71732,7 @@
         <v>45114</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71805,7 +71805,7 @@
         <v>45440</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71878,7 +71878,7 @@
         <v>44825</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71951,7 +71951,7 @@
         <v>45070</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72024,7 +72024,7 @@
         <v>44741</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72102,7 +72102,7 @@
         <v>45688</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72175,7 +72175,7 @@
         <v>45743</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72248,7 +72248,7 @@
         <v>45743</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72321,7 +72321,7 @@
         <v>45743</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72394,7 +72394,7 @@
         <v>45743</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72467,7 +72467,7 @@
         <v>46127</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72540,7 +72540,7 @@
         <v>46147</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>46053</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>46258</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>45257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45596</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>46006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45898</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>46167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45799</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46297</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46064</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46262</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45028</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44852</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46170</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45119</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45394</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44553</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45926</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46057</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44727</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45890</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46274</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>46276</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>46282</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45243</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45120</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45761</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>46045</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45922</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>46064</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45935</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45236</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45955</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45334</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45747</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46258</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45733</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46293</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>46248</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46296</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44582</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44538</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>46049</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>46055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45439</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45945</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45945</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45356</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45096</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45971</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45820</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45989</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45992</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45564</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45827</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45644</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>46164</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>46175</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>46183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>46191</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46206</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45114</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44525</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>46210</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45243</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46258</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46220</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46262</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>46266</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>46225</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>46272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>46276</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46280</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>46237</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45625</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46283</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45119</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45450</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45565</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45768</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45987</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>44866</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44536</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44538</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>44747</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44498</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>44857</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>44777</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44495</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44816</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>44582</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44599</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44481</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>44502</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44489</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44538</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44543</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>44592</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44742</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44816</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44811</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>44499</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>44708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>44817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44496</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44818</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44590</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44820</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44816</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44886</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44590</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44538</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44480</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>44735</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44700</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44571</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45601</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45440</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45478</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45532</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45532</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45265</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45747</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45684</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45363</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44984</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44941</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45363</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45548</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45670</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45511</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45418</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45600</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45350</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45350</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45523</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>44708</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45254</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45425</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44538</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45180</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>46002</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45264</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45414</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45576</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44895</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44806</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45208</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>46002</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>46006</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>46006</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46006</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46006</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46006</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45167</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>46006</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46006</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45377</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45930</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45544</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46008</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46008</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45926</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45926</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45356</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>46010</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>46013</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46010</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45926</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46013</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45938</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45936</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45769</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45586</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>45764</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45586</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45891</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44859</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45309</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45691</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45894</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45141</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45894</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46031</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45896</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45897</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45345</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45110</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45951</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44795</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45145</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46036</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>46036</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45880</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45376</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45905</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45219</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>46038</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45904</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>46038</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46043</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>46043</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44792</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>46042</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46042</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46042</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45219</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45313</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45631</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45230</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44538</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45911</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46045</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46044</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46044</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45912</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46048</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>46049</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45379</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45916</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45467</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>46050</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44592</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45800</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46051</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45644</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46051</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45215</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45347</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45807</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45553</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45090</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45922</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45257</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45925</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45925</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45924</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45262</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45924</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45681</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45924</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46057</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45183</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45929</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>44977</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45350</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45929</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45929</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45929</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45926</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46058</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45929</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45323</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45230</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45935</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45935</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45935</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45604</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46068</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45574</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45484</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45940</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45940</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45940</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44890</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45944</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45783</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45187</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>45945</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45585</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45324</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45945</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45946</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>44531</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45950</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>46080</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45951</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>44950</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45245</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45953</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46083</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>45952</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>45957</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45957</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>45955</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45956</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45642</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45955</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45955</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45952</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45955</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46087</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46087</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45097</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45568</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45959</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45503</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45960</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46092</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45960</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45043</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45559</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45964</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45287</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>44685</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45244</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45574</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45574</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44615</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45559</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45559</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45188</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45971</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45457</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45968</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45635</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44756</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45285</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45975</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45978</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45685</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45618</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45981</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45980</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45985</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45985</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45982</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45982</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46036</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45488</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45986</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45167</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45986</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45824</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45244</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45701</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45988</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45989</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>44722</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>46122</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45827</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45531</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45574</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45574</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44782</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45462</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45995</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45742</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45741</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45993</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45995</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45700</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45642</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>46135</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>46135</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45832</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>46135</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45678</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45834</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45467</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45937</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45247</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45225</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45819</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45936</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45239</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45904</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45098</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45641</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45833</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45848</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45323</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45898</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45849</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45946</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45664</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45848</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45684</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45523</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45848</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45849</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45862</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45714</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45376</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>45760</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>45831</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46136</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>45827</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>45098</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>45370</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45237</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45894</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45324</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45901</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45936</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45965</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45237</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>44874</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45908</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45799</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45393</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44685</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45376</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45828</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45573</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45924</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45334</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45180</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45375</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45664</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>44596</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44623</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44588</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44879</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45911</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>44824</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>44516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>44608</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45797</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44879</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44775</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>44741</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>44741</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45552</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44687</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44523</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45646</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45842</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>44917</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45972</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45642</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45345</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45769</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45890</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45553</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45934</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45419</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>45985</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45478</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45942</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45958</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45544</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45232</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>45021</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45271</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45573</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45924</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45631</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>46140</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45776</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45873</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>46142</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45642</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>44525</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45419</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>45139</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45442</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45625</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46150</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46150</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>46153</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45097</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>46150</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>46150</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45265</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>45596</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45106</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>45175</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45239</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>46154</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>46161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45874</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45874</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46161</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45912</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>44656</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>46162</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44550</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>46162</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45308</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45478</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45478</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45695</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45987</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45035</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45035</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>45881</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45955</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45620</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45400</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45700</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45188</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45877</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45478</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45705</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45880</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>46168</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>46168</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>45726</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45880</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45129</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45541</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>45278</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>46171</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>46177</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46177</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45618</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>45883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>46175</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>46177</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>46177</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>46036</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45644</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>46177</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>46178</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>46177</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45558</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>46183</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>46183</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>46183</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>46188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45434</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>46190</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45605</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45202</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45772</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>46197</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>46195</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>46197</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44529</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45215</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>45706</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>45741</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>44929</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>44929</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>45537</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45644</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45526</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>45601</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>46203</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>46203</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>46203</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45484</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>46203</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>46205</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53963,7 +53963,7 @@
         <v>45015</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>46206</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>46205</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45553</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>45285</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45243</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>46210</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45243</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>46210</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>44817</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>44817</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45434</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>46212</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46197</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55015,7 +55015,7 @@
         <v>46212</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>46212</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>46211</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>46212</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>46212</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>46206</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44539</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45582</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45120</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45120</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46258</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>46258</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55931,7 +55931,7 @@
         <v>45578</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>46217</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45546</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56160,7 +56160,7 @@
         <v>46217</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>44984</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>46260</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>46217</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>46191</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45681</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>46261</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>46111</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45974</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>46262</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56910,7 +56910,7 @@
         <v>46262</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         <v>46262</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57061,7 +57061,7 @@
         <v>45987</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45188</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>46191</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57305,7 +57305,7 @@
         <v>46265</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>46265</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57451,7 +57451,7 @@
         <v>46265</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>46266</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46266</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>46267</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57748,7 +57748,7 @@
         <v>46223</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>46223</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>46223</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>46223</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>46267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>45419</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>46223</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58264,7 +58264,7 @@
         <v>45545</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>46266</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>46266</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>46266</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46226</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45688</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>46268</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45579</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45579</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>45579</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59004,7 +59004,7 @@
         <v>45579</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>46226</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>46268</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>46268</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45222</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59379,7 +59379,7 @@
         <v>46272</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>44685</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>46126</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45505</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>46268</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46268</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46272</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46230</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>46272</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>46272</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>46272</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         <v>46268</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60295,7 +60295,7 @@
         <v>46272</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>46273</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>46274</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>46275</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>45749</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>46276</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>45630</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>46237</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46237</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>46280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>46237</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61201,7 +61201,7 @@
         <v>46237</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61274,7 +61274,7 @@
         <v>46230</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>46230</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>46280</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>46238</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46230</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>45239</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46237</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>44942</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46283</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>44813</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45677</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>46281</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62165,7 +62165,7 @@
         <v>46283</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62243,7 +62243,7 @@
         <v>46275</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62316,7 +62316,7 @@
         <v>45559</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62389,7 +62389,7 @@
         <v>46275</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62462,7 +62462,7 @@
         <v>46286</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>46286</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45593</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62691,7 +62691,7 @@
         <v>45117</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62769,7 +62769,7 @@
         <v>45981</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62842,7 +62842,7 @@
         <v>44890</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>46287</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62988,7 +62988,7 @@
         <v>46285</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45401</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>46244</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>45273</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46154</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63353,7 +63353,7 @@
         <v>46244</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>46244</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63509,7 +63509,7 @@
         <v>45187</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>46244</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>46267</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63733,7 +63733,7 @@
         <v>46245</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>46245</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63879,7 +63879,7 @@
         <v>45491</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63952,7 +63952,7 @@
         <v>46245</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>46245</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64098,7 +64098,7 @@
         <v>46288</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64171,7 +64171,7 @@
         <v>46245</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64244,7 +64244,7 @@
         <v>46248</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>46293</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64400,7 +64400,7 @@
         <v>45245</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>46293</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>45903</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>46247</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>46290</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>45527</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>45527</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64931,7 +64931,7 @@
         <v>46293</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>46247</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65077,7 +65077,7 @@
         <v>46247</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65150,7 +65150,7 @@
         <v>45098</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65223,7 +65223,7 @@
         <v>45639</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         <v>46247</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65369,7 +65369,7 @@
         <v>45239</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65442,7 +65442,7 @@
         <v>45559</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>45603</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65588,7 +65588,7 @@
         <v>46251</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65661,7 +65661,7 @@
         <v>46252</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>46252</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65885,7 +65885,7 @@
         <v>44785</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65958,7 +65958,7 @@
         <v>46294</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46252</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         <v>46294</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45211</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66255,7 +66255,7 @@
         <v>46297</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66328,7 +66328,7 @@
         <v>46297</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66401,7 +66401,7 @@
         <v>45167</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>45090</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66552,7 +66552,7 @@
         <v>46297</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66625,7 +66625,7 @@
         <v>45043</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66698,7 +66698,7 @@
         <v>45607</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66771,7 +66771,7 @@
         <v>46296</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66849,7 +66849,7 @@
         <v>46252</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66922,7 +66922,7 @@
         <v>46230</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66995,7 +66995,7 @@
         <v>45125</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67068,7 +67068,7 @@
         <v>45125</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67141,7 +67141,7 @@
         <v>46254</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67214,7 +67214,7 @@
         <v>44888</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67287,7 +67287,7 @@
         <v>45478</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67360,7 +67360,7 @@
         <v>45478</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67433,7 +67433,7 @@
         <v>44622</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>46296</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67579,7 +67579,7 @@
         <v>46255</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67652,7 +67652,7 @@
         <v>44942</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67725,7 +67725,7 @@
         <v>46254</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67803,7 +67803,7 @@
         <v>46297</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67876,7 +67876,7 @@
         <v>46297</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>46254</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68032,7 +68032,7 @@
         <v>46254</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68105,7 +68105,7 @@
         <v>45420</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68178,7 +68178,7 @@
         <v>45610</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68256,7 +68256,7 @@
         <v>45140</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68334,7 +68334,7 @@
         <v>45627</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>44658</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68480,7 +68480,7 @@
         <v>45176</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45273</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68626,7 +68626,7 @@
         <v>44874</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68704,7 +68704,7 @@
         <v>45238</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68777,7 +68777,7 @@
         <v>44971</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>44708</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68923,7 +68923,7 @@
         <v>45596</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69001,7 +69001,7 @@
         <v>45617</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69079,7 +69079,7 @@
         <v>44907</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69152,7 +69152,7 @@
         <v>45229</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69230,7 +69230,7 @@
         <v>45273</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69303,7 +69303,7 @@
         <v>45331</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69376,7 +69376,7 @@
         <v>45741</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69449,7 +69449,7 @@
         <v>45741</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69522,7 +69522,7 @@
         <v>45312</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69595,7 +69595,7 @@
         <v>45316</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69668,7 +69668,7 @@
         <v>45244</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69741,7 +69741,7 @@
         <v>45056</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69814,7 +69814,7 @@
         <v>45056</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69887,7 +69887,7 @@
         <v>44813</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -69960,7 +69960,7 @@
         <v>45251</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70033,7 +70033,7 @@
         <v>45254</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70106,7 +70106,7 @@
         <v>45646</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70179,7 +70179,7 @@
         <v>44972</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70252,7 +70252,7 @@
         <v>45687</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70325,7 +70325,7 @@
         <v>44817</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70403,7 +70403,7 @@
         <v>45138</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70476,7 +70476,7 @@
         <v>45028</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70549,7 +70549,7 @@
         <v>45177</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70622,7 +70622,7 @@
         <v>45776</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70695,7 +70695,7 @@
         <v>45405</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45434</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70841,7 +70841,7 @@
         <v>45357</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70914,7 +70914,7 @@
         <v>45782</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -70987,7 +70987,7 @@
         <v>45782</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71060,7 +71060,7 @@
         <v>45783</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71138,7 +71138,7 @@
         <v>45090</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71211,7 +71211,7 @@
         <v>45462</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71284,7 +71284,7 @@
         <v>45110</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71357,7 +71357,7 @@
         <v>45315</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71430,7 +71430,7 @@
         <v>45315</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71503,7 +71503,7 @@
         <v>45476</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71576,7 +71576,7 @@
         <v>45113</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71654,7 +71654,7 @@
         <v>45013</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71732,7 +71732,7 @@
         <v>45114</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71805,7 +71805,7 @@
         <v>45440</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71878,7 +71878,7 @@
         <v>44825</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -71951,7 +71951,7 @@
         <v>45070</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72024,7 +72024,7 @@
         <v>44741</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72102,7 +72102,7 @@
         <v>45688</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72175,7 +72175,7 @@
         <v>45743</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72248,7 +72248,7 @@
         <v>45743</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72321,7 +72321,7 @@
         <v>45743</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72394,7 +72394,7 @@
         <v>45743</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72467,7 +72467,7 @@
         <v>46127</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72540,7 +72540,7 @@
         <v>46147</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46053</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>46167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45799</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46297</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>46064</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46262</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45028</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44852</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>46170</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45394</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45446</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44553</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45243</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45925</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45926</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45890</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46057</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>46064</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>46276</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>46282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45761</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45334</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45955</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45546</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45733</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45236</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>46248</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>46293</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46296</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>46301</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>46258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44538</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45119</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45114</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45564</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45450</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45918</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44525</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45491</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45565</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45625</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45439</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45945</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45243</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>45945</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>45971</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44525</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45992</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45989</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>46008</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45827</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>46049</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>46164</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46167</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>46175</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>46183</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>46191</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>46206</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>46210</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46266</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>46220</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46225</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>46272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46276</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46237</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>46280</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>46283</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46302</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>46258</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>46262</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44636</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45768</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45987</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>46184</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44866</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44536</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44538</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44857</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>44495</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44777</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>44816</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44848</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44582</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44599</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44481</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44502</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44489</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>44818</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>44538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44590</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44616</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44543</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44480</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44820</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44708</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>44742</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44816</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44590</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44811</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44499</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44816</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44496</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>44735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45345</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44571</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45363</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44972</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45309</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45419</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45167</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45356</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>44817</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45537</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45620</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44888</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45523</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45225</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45558</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>44813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45376</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>44890</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45177</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>44813</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45090</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45285</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45312</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45254</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45239</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45110</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44824</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45478</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45478</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45334</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45043</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45271</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45350</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44942</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45582</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45257</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45457</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45350</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45467</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45264</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45418</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44685</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>44550</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45363</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45376</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45574</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45574</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45726</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44708</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45883</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45167</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45625</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45139</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45377</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44874</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45237</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45237</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45579</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45579</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45140</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45247</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45117</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>45331</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45478</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45229</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45273</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44950</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45467</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45440</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45618</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45769</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45376</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45324</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45505</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45478</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45559</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45544</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45891</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45894</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45896</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45278</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45462</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45897</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45573</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45281</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45631</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45180</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45488</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45532</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45532</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45434</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45511</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45273</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45125</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45125</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45574</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44539</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45559</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45559</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45904</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45880</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45610</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45639</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45635</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45904</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45905</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44592</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45627</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45912</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45273</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45912</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45747</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45545</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45357</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45405</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45239</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45618</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45434</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45782</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45782</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45783</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44608</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45644</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45491</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45916</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45315</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45315</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45090</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45110</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>45503</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45741</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45401</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45701</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45527</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45462</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45924</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45120</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45120</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45527</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45578</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45576</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44806</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45015</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45141</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45925</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45791</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45531</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44795</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45929</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45929</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45929</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45929</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45230</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45631</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45929</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45145</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45219</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>45420</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45630</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45313</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45559</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>45596</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45264</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45478</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44538</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45208</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45244</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45028</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45187</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45644</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45541</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45230</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45285</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45935</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45419</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45935</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45601</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45467</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44622</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45379</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45056</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45800</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45043</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45935</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45605</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>45548</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45345</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>44977</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45684</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45347</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45553</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44658</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44531</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45807</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>44685</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>44782</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45940</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45090</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45585</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45687</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45940</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45940</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45944</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45600</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45188</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45553</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45239</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45568</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45783</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45945</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45741</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45741</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45945</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>44941</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45706</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45238</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45946</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45950</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45138</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45175</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>44756</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44656</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45574</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45098</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>45824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45323</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>44817</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45642</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45098</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45827</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45832</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45700</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45243</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45243</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44722</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45951</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45952</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45177</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>45952</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45953</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45955</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>45955</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45955</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45955</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45956</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45957</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45957</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45960</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>45960</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45960</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45960</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>45960</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45959</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45644</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>44683</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45642</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45642</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45964</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45834</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44929</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44929</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>44911</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>44907</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44792</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>45968</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45129</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>45414</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45695</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>45971</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45971</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45553</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45215</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45971</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45681</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45244</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45245</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>44859</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45848</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45974</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45848</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45167</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45849</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45320</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45978</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45183</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45828</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45573</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45799</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>44741</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>44879</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>44879</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>44741</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44516</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44523</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44588</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44687</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>44775</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>44623</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>44596</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45769</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45219</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45098</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44890</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45544</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45251</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45975</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45188</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45287</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>45442</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45980</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45677</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45873</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45685</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45874</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45478</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45874</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45880</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45981</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45880</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45265</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>45982</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45982</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45981</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45981</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>44785</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45484</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>44895</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45670</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45324</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>44685</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45526</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45187</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45985</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45985</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45273</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>45239</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45986</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45986</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45688</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45484</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45265</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45985</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45393</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45985</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44874</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>44984</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45579</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45579</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45523</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45601</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44971</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45552</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>45180</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45646</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45772</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45678</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>45988</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45701</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>46036</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45989</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45262</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45646</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45559</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>44525</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45993</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45546</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45993</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45742</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>45741</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45995</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45995</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>46122</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>46126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45952</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>46002</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>46002</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>46006</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>46006</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>46006</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>46006</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>46006</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>46006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>46006</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49585,7 +49585,7 @@
         <v>46006</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>46006</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49731,7 +49731,7 @@
         <v>46135</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45419</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>44615</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>46008</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46008</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45642</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>46136</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>46135</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45926</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>46135</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45604</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>46010</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45316</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>46010</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45926</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45926</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45930</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>46013</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45842</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45898</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51196,7 +51196,7 @@
         <v>45176</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>46013</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51342,7 +51342,7 @@
         <v>45936</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51415,7 +51415,7 @@
         <v>45951</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45986</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45938</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45936</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45936</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45936</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45936</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45586</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45586</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45425</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>45603</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>45596</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>45641</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45691</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>45593</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45021</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>45776</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45375</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45924</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45936</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>44917</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>45323</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45106</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45245</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45985</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45831</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45958</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>44942</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45972</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>44708</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45664</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>45862</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45951</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45946</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45936</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>46031</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45760</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45849</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>46034</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>46036</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>46036</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>45924</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45714</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>46036</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>44538</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45827</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>45833</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>46038</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>46042</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>46042</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>46042</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>46042</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>46042</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45894</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45211</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45797</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>46038</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45908</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>46044</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>46044</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45848</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>45664</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45097</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45370</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>46043</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>45901</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45819</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>46043</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46048</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>45478</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>45965</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46048</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45904</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45684</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>45890</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>45254</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
         <v>45937</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>46140</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>46045</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45942</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45232</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>45911</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46142</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>45934</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45350</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45607</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>45308</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>46049</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>46050</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>46051</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>46051</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58254,7 +58254,7 @@
         <v>46057</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>46058</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>46068</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46150</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46150</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>46150</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>46150</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>46153</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>46154</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58911,7 +58911,7 @@
         <v>46080</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58984,7 +58984,7 @@
         <v>46083</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>46087</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>46087</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>45912</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59281,7 +59281,7 @@
         <v>46161</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>46092</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59427,7 +59427,7 @@
         <v>45244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>45987</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>46162</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59646,7 +59646,7 @@
         <v>46161</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59719,7 +59719,7 @@
         <v>46162</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>45955</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45881</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59938,7 +59938,7 @@
         <v>45400</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45700</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>46168</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60157,7 +60157,7 @@
         <v>46168</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60230,7 +60230,7 @@
         <v>46171</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60308,7 +60308,7 @@
         <v>46177</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>46177</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>46177</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60527,7 +60527,7 @@
         <v>46177</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>46177</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60673,7 +60673,7 @@
         <v>46177</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>46036</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>46178</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60897,7 +60897,7 @@
         <v>46183</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>46183</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>46183</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46188</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61209,7 +61209,7 @@
         <v>46190</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>46195</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61360,7 +61360,7 @@
         <v>46197</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61433,7 +61433,7 @@
         <v>46197</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>46203</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>46203</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>46203</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>46203</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61803,7 +61803,7 @@
         <v>46205</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>46205</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>46206</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>46211</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62110,7 +62110,7 @@
         <v>46197</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>46210</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62261,7 +62261,7 @@
         <v>46210</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62339,7 +62339,7 @@
         <v>46212</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>46212</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>46212</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>46212</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62641,7 +62641,7 @@
         <v>46212</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62719,7 +62719,7 @@
         <v>46217</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>46217</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>46206</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>46217</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>46191</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>46223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63172,7 +63172,7 @@
         <v>46266</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>46266</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>46266</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>46191</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>46266</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>46223</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>45987</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63703,7 +63703,7 @@
         <v>46223</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63776,7 +63776,7 @@
         <v>46223</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>46111</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
         <v>46223</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63995,7 +63995,7 @@
         <v>45974</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>46265</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>46265</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>46266</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64287,7 +64287,7 @@
         <v>46268</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         <v>46268</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         <v>46267</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>46267</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64589,7 +64589,7 @@
         <v>46265</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>46272</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64740,7 +64740,7 @@
         <v>46226</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64818,7 +64818,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64896,7 +64896,7 @@
         <v>46268</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64974,7 +64974,7 @@
         <v>46268</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65052,7 +65052,7 @@
         <v>46126</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         <v>46272</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65203,7 +65203,7 @@
         <v>46272</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65281,7 +65281,7 @@
         <v>46268</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65359,7 +65359,7 @@
         <v>46226</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>46272</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>46272</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65583,7 +65583,7 @@
         <v>46272</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65661,7 +65661,7 @@
         <v>46273</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>46230</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65890,7 +65890,7 @@
         <v>45749</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65963,7 +65963,7 @@
         <v>46276</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66041,7 +66041,7 @@
         <v>46275</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66114,7 +66114,7 @@
         <v>46237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66187,7 +66187,7 @@
         <v>46237</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>46237</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>46237</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66416,7 +66416,7 @@
         <v>46280</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>46280</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>46237</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66635,7 +66635,7 @@
         <v>46280</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>46238</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>46230</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66864,7 +66864,7 @@
         <v>46283</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66942,7 +66942,7 @@
         <v>46285</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67015,7 +67015,7 @@
         <v>46154</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>46286</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67166,7 +67166,7 @@
         <v>46275</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67239,7 +67239,7 @@
         <v>46275</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67312,7 +67312,7 @@
         <v>46283</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67385,7 +67385,7 @@
         <v>46281</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>46286</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67541,7 +67541,7 @@
         <v>46245</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67614,7 +67614,7 @@
         <v>46245</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>45981</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67760,7 +67760,7 @@
         <v>46245</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67833,7 +67833,7 @@
         <v>46245</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>46244</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>46288</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68052,7 +68052,7 @@
         <v>46244</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>46245</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68203,7 +68203,7 @@
         <v>46244</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68281,7 +68281,7 @@
         <v>46267</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68359,7 +68359,7 @@
         <v>46287</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68432,7 +68432,7 @@
         <v>46244</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68505,7 +68505,7 @@
         <v>46247</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68578,7 +68578,7 @@
         <v>46290</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68656,7 +68656,7 @@
         <v>46247</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68729,7 +68729,7 @@
         <v>46247</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68802,7 +68802,7 @@
         <v>46247</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68875,7 +68875,7 @@
         <v>46293</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68953,7 +68953,7 @@
         <v>46293</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69031,7 +69031,7 @@
         <v>46294</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>46294</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69177,7 +69177,7 @@
         <v>46293</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>46248</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69328,7 +69328,7 @@
         <v>45903</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69401,7 +69401,7 @@
         <v>46252</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>46251</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>46296</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69625,7 +69625,7 @@
         <v>46252</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>46252</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69776,7 +69776,7 @@
         <v>46296</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46251</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69927,7 +69927,7 @@
         <v>46297</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70000,7 +70000,7 @@
         <v>46254</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70078,7 +70078,7 @@
         <v>46255</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70151,7 +70151,7 @@
         <v>46297</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70224,7 +70224,7 @@
         <v>46230</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>46254</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         <v>46297</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>46297</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70521,7 +70521,7 @@
         <v>46297</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70594,7 +70594,7 @@
         <v>46254</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70667,7 +70667,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70745,7 +70745,7 @@
         <v>46230</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70818,7 +70818,7 @@
         <v>46230</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70891,7 +70891,7 @@
         <v>46252</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70964,7 +70964,7 @@
         <v>46301</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>46301</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>46301</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>46301</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71271,7 +71271,7 @@
         <v>46258</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>46258</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71427,7 +71427,7 @@
         <v>46301</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71505,7 +71505,7 @@
         <v>46301</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71583,7 +71583,7 @@
         <v>46261</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71661,7 +71661,7 @@
         <v>46262</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>46260</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71812,7 +71812,7 @@
         <v>46303</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71885,7 +71885,7 @@
         <v>46262</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71963,7 +71963,7 @@
         <v>46262</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72036,7 +72036,7 @@
         <v>46303</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72109,7 +72109,7 @@
         <v>45776</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72182,7 +72182,7 @@
         <v>45476</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72255,7 +72255,7 @@
         <v>45113</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72333,7 +72333,7 @@
         <v>45013</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72411,7 +72411,7 @@
         <v>45114</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72484,7 +72484,7 @@
         <v>45440</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72557,7 +72557,7 @@
         <v>44825</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72630,7 +72630,7 @@
         <v>45070</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72703,7 +72703,7 @@
         <v>44741</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72781,7 +72781,7 @@
         <v>45688</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72854,7 +72854,7 @@
         <v>45743</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72927,7 +72927,7 @@
         <v>45743</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73000,7 +73000,7 @@
         <v>45743</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73073,7 +73073,7 @@
         <v>45743</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73146,7 +73146,7 @@
         <v>46127</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73219,7 +73219,7 @@
         <v>46147</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46053</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>46167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45799</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46297</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>46064</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46262</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45028</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44852</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>46170</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45394</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45446</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44553</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45243</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45925</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45926</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45890</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46057</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>46064</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>46276</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>46282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45761</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45334</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45955</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45546</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45733</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45236</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>46248</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>46293</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46296</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>46301</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>46258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44538</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45119</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45114</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45564</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45450</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45918</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44525</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45491</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45565</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45625</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45439</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45945</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45243</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>45945</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>45971</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44525</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45992</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45989</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>46008</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45827</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>46049</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>46164</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46167</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>46175</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>46183</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>46191</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>46206</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>46210</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46266</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>46220</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46225</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>46272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46276</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46237</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>46280</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>46283</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46302</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>46258</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>46262</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44636</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45768</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45987</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>46184</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44866</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44536</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44538</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44857</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>44495</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44777</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>44816</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44848</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44582</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44599</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44481</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44502</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44489</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>44818</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>44538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44590</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44616</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44543</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44480</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44820</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44708</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>44742</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44816</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44590</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44811</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44499</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44816</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44496</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>44735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45345</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44571</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45363</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44972</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45309</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45419</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45167</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45356</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>44817</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45537</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45620</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44888</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45523</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45225</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45558</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>44813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45376</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>44890</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45177</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>44813</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45090</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45285</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45312</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45254</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45239</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45110</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44824</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45478</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45478</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45334</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45043</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45271</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45350</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44942</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45582</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45257</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45457</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45350</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45467</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45264</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45418</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44685</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>44550</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45363</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45376</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45574</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45574</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45726</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44708</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45883</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45167</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45625</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45139</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45377</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44874</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45237</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45237</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45579</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45579</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45140</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45247</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45117</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>45331</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45478</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45229</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45273</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44950</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45467</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45440</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45618</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45769</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45376</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45324</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45505</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45478</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45559</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45544</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45891</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45894</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45896</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45278</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45462</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45897</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45573</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45281</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45631</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45180</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45488</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45532</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45532</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45434</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45511</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45273</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45125</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45125</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45574</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44539</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45559</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45559</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45904</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45880</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45610</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45639</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45635</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45904</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45905</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44592</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45627</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45912</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45273</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45912</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45747</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45545</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45357</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45405</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45239</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45618</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45434</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45782</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45782</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45783</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44608</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45644</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45491</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45916</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45315</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45315</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45090</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45110</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>45503</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45741</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45401</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45701</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45527</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45462</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45924</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45120</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45120</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45527</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45578</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45576</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44806</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45015</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45141</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45925</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45791</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45531</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44795</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45929</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45929</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45929</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45929</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45230</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45631</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45929</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45145</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45219</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>45420</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45630</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45313</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45559</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>45596</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45264</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45478</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44538</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45208</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45244</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45028</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45187</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45644</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45541</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45230</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45285</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45935</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45419</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45935</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45601</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45467</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44622</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45379</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45056</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45800</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45043</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45935</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45605</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>45548</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45345</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>44977</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45684</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45347</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45553</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44658</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44531</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45807</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>44685</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>44782</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45940</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45090</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45585</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45687</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45940</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45940</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45944</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45600</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45188</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45553</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45239</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45568</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45783</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45945</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45741</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45741</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45945</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>44941</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45706</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45238</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45946</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45950</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45138</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45175</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>44756</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44656</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45574</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45098</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>45824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45323</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>44817</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45642</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45098</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45827</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45832</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45700</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45243</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45243</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44722</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45951</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45952</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45177</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>45952</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45953</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45955</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>45955</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45955</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45955</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45956</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45957</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45957</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45960</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>45960</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45960</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45960</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>45960</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45959</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45644</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>44683</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45642</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45642</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45964</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45834</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44929</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44929</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>44911</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>44907</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44792</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>45968</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45129</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>45414</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45695</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>45971</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45971</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45553</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45215</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45971</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45681</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45244</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45245</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>44859</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45848</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45974</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45848</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45167</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45849</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45320</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45978</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45183</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45828</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45573</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45799</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>44741</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>44879</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>44879</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>44741</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44516</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44523</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44588</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44687</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>44775</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>44623</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>44596</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45769</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45219</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45098</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44890</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45544</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45251</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45975</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45188</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45287</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>45442</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45980</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45677</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45873</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45685</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45874</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45478</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45874</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45880</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45981</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45880</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45265</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>45982</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45982</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45981</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45981</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>44785</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45484</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>44895</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45670</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45324</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>44685</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45526</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45187</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45985</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45985</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45273</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>45239</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45986</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45986</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45688</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45484</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45265</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45985</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45393</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45985</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44874</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>44984</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45579</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45579</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45523</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45601</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44971</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45552</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>45180</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45646</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45772</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45678</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>45988</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45701</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>46036</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45989</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45262</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45646</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45559</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>44525</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45993</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45546</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45993</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45742</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>45741</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45995</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45995</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>46122</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>46126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45952</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>46002</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>46002</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>46006</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>46006</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>46006</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>46006</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>46006</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>46006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>46006</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49585,7 +49585,7 @@
         <v>46006</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>46006</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49731,7 +49731,7 @@
         <v>46135</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45419</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>44615</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>46008</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46008</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45642</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>46136</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>46135</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45926</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>46135</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45604</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>46010</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45316</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>46010</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45926</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45926</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45930</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>46013</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45842</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45898</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51196,7 +51196,7 @@
         <v>45176</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>46013</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51342,7 +51342,7 @@
         <v>45936</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51415,7 +51415,7 @@
         <v>45951</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45986</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45938</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45936</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45936</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45936</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45936</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45586</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45586</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45425</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>45603</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>45596</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>45641</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45691</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>45593</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45021</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>45776</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45375</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45924</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45936</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>44917</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>45323</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45106</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45245</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45985</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45831</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45958</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>44942</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45972</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>44708</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45664</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>45862</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45951</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45946</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45936</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>46031</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45760</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45849</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>46034</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>46036</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>46036</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>45924</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45714</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>46036</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>44538</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45827</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>45833</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>46038</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>46042</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>46042</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>46042</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>46042</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>46042</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45894</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45211</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45797</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>46038</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45908</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>46044</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>46044</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45848</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>45664</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45097</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45370</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>46043</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>45901</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45819</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>46043</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46048</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>45478</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>45965</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46048</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45904</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45684</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>45890</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>45254</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
         <v>45937</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>46140</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>46045</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45942</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45232</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>45911</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46142</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>45934</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45350</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45607</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>45308</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>46049</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>46050</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>46051</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>46051</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58254,7 +58254,7 @@
         <v>46057</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>46058</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>46068</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46150</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46150</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>46150</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>46150</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>46153</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>46154</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58911,7 +58911,7 @@
         <v>46080</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58984,7 +58984,7 @@
         <v>46083</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>46087</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>46087</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>45912</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59281,7 +59281,7 @@
         <v>46161</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>46092</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59427,7 +59427,7 @@
         <v>45244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>45987</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>46162</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59646,7 +59646,7 @@
         <v>46161</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59719,7 +59719,7 @@
         <v>46162</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>45955</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45881</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59938,7 +59938,7 @@
         <v>45400</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45700</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>46168</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60157,7 +60157,7 @@
         <v>46168</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60230,7 +60230,7 @@
         <v>46171</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60308,7 +60308,7 @@
         <v>46177</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>46177</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>46177</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60527,7 +60527,7 @@
         <v>46177</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>46177</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60673,7 +60673,7 @@
         <v>46177</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>46036</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>46178</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60897,7 +60897,7 @@
         <v>46183</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>46183</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>46183</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46188</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61209,7 +61209,7 @@
         <v>46190</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>46195</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61360,7 +61360,7 @@
         <v>46197</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61433,7 +61433,7 @@
         <v>46197</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>46203</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>46203</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>46203</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>46203</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61803,7 +61803,7 @@
         <v>46205</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>46205</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>46206</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>46211</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62110,7 +62110,7 @@
         <v>46197</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>46210</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62261,7 +62261,7 @@
         <v>46210</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62339,7 +62339,7 @@
         <v>46212</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>46212</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>46212</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>46212</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62641,7 +62641,7 @@
         <v>46212</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62719,7 +62719,7 @@
         <v>46217</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>46217</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>46206</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>46217</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>46191</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>46223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63172,7 +63172,7 @@
         <v>46266</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>46266</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>46266</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>46191</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>46266</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>46223</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>45987</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63703,7 +63703,7 @@
         <v>46223</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63776,7 +63776,7 @@
         <v>46223</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>46111</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
         <v>46223</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63995,7 +63995,7 @@
         <v>45974</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>46265</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>46265</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>46266</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64287,7 +64287,7 @@
         <v>46268</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         <v>46268</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         <v>46267</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>46267</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64589,7 +64589,7 @@
         <v>46265</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>46272</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64740,7 +64740,7 @@
         <v>46226</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64818,7 +64818,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64896,7 +64896,7 @@
         <v>46268</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64974,7 +64974,7 @@
         <v>46268</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65052,7 +65052,7 @@
         <v>46126</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         <v>46272</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65203,7 +65203,7 @@
         <v>46272</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65281,7 +65281,7 @@
         <v>46268</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65359,7 +65359,7 @@
         <v>46226</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>46272</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>46272</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65583,7 +65583,7 @@
         <v>46272</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65661,7 +65661,7 @@
         <v>46273</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>46230</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65890,7 +65890,7 @@
         <v>45749</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65963,7 +65963,7 @@
         <v>46276</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66041,7 +66041,7 @@
         <v>46275</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66114,7 +66114,7 @@
         <v>46237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66187,7 +66187,7 @@
         <v>46237</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>46237</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>46237</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66416,7 +66416,7 @@
         <v>46280</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>46280</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>46237</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66635,7 +66635,7 @@
         <v>46280</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>46238</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>46230</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66864,7 +66864,7 @@
         <v>46283</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66942,7 +66942,7 @@
         <v>46285</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67015,7 +67015,7 @@
         <v>46154</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>46286</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67166,7 +67166,7 @@
         <v>46275</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67239,7 +67239,7 @@
         <v>46275</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67312,7 +67312,7 @@
         <v>46283</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67385,7 +67385,7 @@
         <v>46281</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>46286</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67541,7 +67541,7 @@
         <v>46245</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67614,7 +67614,7 @@
         <v>46245</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>45981</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67760,7 +67760,7 @@
         <v>46245</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67833,7 +67833,7 @@
         <v>46245</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>46244</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>46288</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68052,7 +68052,7 @@
         <v>46244</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>46245</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68203,7 +68203,7 @@
         <v>46244</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68281,7 +68281,7 @@
         <v>46267</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68359,7 +68359,7 @@
         <v>46287</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68432,7 +68432,7 @@
         <v>46244</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68505,7 +68505,7 @@
         <v>46247</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68578,7 +68578,7 @@
         <v>46290</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68656,7 +68656,7 @@
         <v>46247</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68729,7 +68729,7 @@
         <v>46247</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68802,7 +68802,7 @@
         <v>46247</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68875,7 +68875,7 @@
         <v>46293</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68953,7 +68953,7 @@
         <v>46293</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69031,7 +69031,7 @@
         <v>46294</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>46294</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69177,7 +69177,7 @@
         <v>46293</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>46248</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69328,7 +69328,7 @@
         <v>45903</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69401,7 +69401,7 @@
         <v>46252</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>46251</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>46296</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69625,7 +69625,7 @@
         <v>46252</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>46252</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69776,7 +69776,7 @@
         <v>46296</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>46251</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -69927,7 +69927,7 @@
         <v>46297</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70000,7 +70000,7 @@
         <v>46254</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70078,7 +70078,7 @@
         <v>46255</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70151,7 +70151,7 @@
         <v>46297</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70224,7 +70224,7 @@
         <v>46230</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>46254</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         <v>46297</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>46297</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70521,7 +70521,7 @@
         <v>46297</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70594,7 +70594,7 @@
         <v>46254</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70667,7 +70667,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70745,7 +70745,7 @@
         <v>46230</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70818,7 +70818,7 @@
         <v>46230</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70891,7 +70891,7 @@
         <v>46252</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -70964,7 +70964,7 @@
         <v>46301</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>46301</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>46301</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>46301</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71271,7 +71271,7 @@
         <v>46258</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>46258</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71427,7 +71427,7 @@
         <v>46301</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71505,7 +71505,7 @@
         <v>46301</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71583,7 +71583,7 @@
         <v>46261</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71661,7 +71661,7 @@
         <v>46262</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>46260</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71812,7 +71812,7 @@
         <v>46303</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71885,7 +71885,7 @@
         <v>46262</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -71963,7 +71963,7 @@
         <v>46262</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72036,7 +72036,7 @@
         <v>46303</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72109,7 +72109,7 @@
         <v>45776</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72182,7 +72182,7 @@
         <v>45476</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72255,7 +72255,7 @@
         <v>45113</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72333,7 +72333,7 @@
         <v>45013</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72411,7 +72411,7 @@
         <v>45114</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72484,7 +72484,7 @@
         <v>45440</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72557,7 +72557,7 @@
         <v>44825</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72630,7 +72630,7 @@
         <v>45070</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72703,7 +72703,7 @@
         <v>44741</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72781,7 +72781,7 @@
         <v>45688</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72854,7 +72854,7 @@
         <v>45743</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -72927,7 +72927,7 @@
         <v>45743</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73000,7 +73000,7 @@
         <v>45743</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73073,7 +73073,7 @@
         <v>45743</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73146,7 +73146,7 @@
         <v>46127</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73219,7 +73219,7 @@
         <v>46147</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>46053</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>46167</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>46274</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>46297</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>45799</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>45701</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>46050</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>46262</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45028</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44852</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46170</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45119</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44553</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44727</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45890</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45925</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45926</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>46274</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>46276</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45491</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45761</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45236</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45334</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45955</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>46045</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>46064</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45202</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45846</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>46217</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46293</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>46248</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>46296</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>46258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46301</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>46258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45789</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44538</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44525</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45439</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45096</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45224</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45564</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45945</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>45971</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45644</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>46164</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>46167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45992</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>46049</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>46055</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45114</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>44525</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46191</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45243</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>46206</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45625</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>46210</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45450</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>46220</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>46272</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>46276</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46280</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>46237</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>46283</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>46258</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45491</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46302</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>46262</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>46175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45356</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45820</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45544</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44636</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45768</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>46184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44866</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44536</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44538</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44747</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44498</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>44857</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>44777</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44495</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44816</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>44848</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44599</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44502</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44489</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44816</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44499</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44817</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44496</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44818</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44590</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>44820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44886</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>44590</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>44538</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44571</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45363</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>45478</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45601</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45532</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>44942</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45440</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>44941</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45747</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45363</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45670</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45523</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45511</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45418</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45350</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45350</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45684</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45254</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45425</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44538</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45576</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45180</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44708</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44806</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45208</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45544</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>44911</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45320</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45356</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45467</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>44859</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45309</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45345</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45110</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45376</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45145</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45219</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44792</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45644</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45414</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45215</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44592</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         <v>45090</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45257</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45183</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>44977</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45350</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45262</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45681</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45604</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45574</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45324</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>44890</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45187</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45484</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45323</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45642</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45503</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45559</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45287</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44685</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45574</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45574</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45457</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44615</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45559</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45559</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45188</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>44756</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45230</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45285</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45685</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45618</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45883</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45849</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45377</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45167</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45946</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45664</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45684</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45244</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45862</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45714</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45760</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45831</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>46136</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45827</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44722</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45370</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45894</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45531</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45574</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>44782</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45462</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45769</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45764</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45901</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45936</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45965</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45891</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>45894</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45908</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45894</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45896</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45897</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45642</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45924</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45375</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45664</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45911</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45797</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45678</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45842</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45972</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>46034</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45890</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45934</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45467</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45478</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45958</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45021</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45880</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45905</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45904</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45904</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45924</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45225</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>46140</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45776</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45911</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45915</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45912</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45098</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45912</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45916</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45281</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45922</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45924</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45924</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45924</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45929</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45376</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45929</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45929</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45929</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45926</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45929</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45098</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45237</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>46150</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>46150</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46153</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46150</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45935</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45935</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45935</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45324</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>46150</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44874</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45393</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45376</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45940</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45940</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45334</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45940</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45180</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45944</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45783</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45945</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>44824</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>45945</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44608</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45946</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45552</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45646</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45950</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44917</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45951</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45953</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45345</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45952</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>46154</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45957</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45955</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45956</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45955</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45955</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45952</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>45553</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>45955</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45959</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45419</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>45245</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45960</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45960</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>46161</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45232</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45960</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45271</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45964</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46161</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45573</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45631</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45912</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45971</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45971</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45968</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45642</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>46162</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44525</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46162</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45419</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45975</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45139</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45978</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45987</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45625</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45097</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45881</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45981</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45981</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45981</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45980</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45985</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>45265</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>45985</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45982</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45596</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45982</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45266</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45264</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45955</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45985</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45985</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45239</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45986</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45700</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>45986</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45988</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>46168</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>46168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45993</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>44656</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>44550</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45308</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45478</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45478</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45995</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45742</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45741</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45695</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45993</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45995</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45035</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45035</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45620</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45952</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45188</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45478</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>46002</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45705</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>46002</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45726</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46006</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>46006</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>46006</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>46006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>46006</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46006</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>46006</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>46006</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>46006</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45930</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45129</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45541</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45278</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>46008</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>46008</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45926</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45926</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46010</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46013</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46010</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45926</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46171</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46013</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45618</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45938</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45951</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45986</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45936</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45644</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45936</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45936</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45936</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45936</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45586</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45586</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45558</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45691</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>46177</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>46177</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>46031</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>45951</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>46177</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>46036</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>46036</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>46036</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46177</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>46036</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>46038</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46038</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>46177</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46178</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>46177</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>46043</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>46042</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46042</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>46042</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45434</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>46042</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>46042</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46042</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>46042</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46045</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45605</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>46044</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>46044</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45202</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45772</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>46048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>46048</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>46049</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>46050</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>46051</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>46051</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>44529</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>46057</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>46183</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45215</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45706</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>46058</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45741</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>46183</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>44929</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>44929</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45537</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>45644</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>46183</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>46188</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>46068</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45526</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45601</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45484</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>46080</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>46083</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45015</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45553</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45285</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45243</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>46087</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>45243</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>46087</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>46190</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>44817</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>44817</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45434</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>46092</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45244</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44539</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45582</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45120</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45120</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45578</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45546</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>46197</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>44984</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>46195</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>46197</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45681</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>46036</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50269,7 +50269,7 @@
         <v>45188</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>45419</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>46122</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45545</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46126</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45688</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>45579</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45579</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45579</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45579</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45222</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>44685</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>46203</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45505</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46203</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46135</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46135</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46135</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>46203</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45630</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45937</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45819</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>46205</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45936</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45239</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45904</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45641</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>44942</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45833</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45848</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44813</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45677</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>46206</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>46205</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46210</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>46210</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>45559</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>45593</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>45117</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46212</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46197</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46212</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>46212</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53551,7 +53551,7 @@
         <v>46211</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46212</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>46212</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>44890</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>46206</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45401</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45273</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54072,7 +54072,7 @@
         <v>46217</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54150,7 +54150,7 @@
         <v>46217</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>46191</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45187</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>46111</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45974</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45987</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>45491</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>46191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46223</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>46223</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46223</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>46223</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>46223</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46226</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>46226</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55280,7 +55280,7 @@
         <v>46272</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>46126</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45245</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46230</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>46272</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>46272</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>46273</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>46274</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>45527</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45527</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>46275</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45098</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>45639</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45749</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45239</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45559</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45603</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>46276</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>46237</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>46237</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46280</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>44785</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>46280</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>46237</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>46237</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57384,7 +57384,7 @@
         <v>46230</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>46280</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45211</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57603,7 +57603,7 @@
         <v>46238</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57681,7 +57681,7 @@
         <v>45167</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45090</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45043</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>46237</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>45607</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>46283</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45125</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>45125</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>46281</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>46283</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58426,7 +58426,7 @@
         <v>46275</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>44888</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>45478</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45478</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>44622</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>46275</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>44942</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>46286</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>46286</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45420</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59166,7 +59166,7 @@
         <v>45981</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59239,7 +59239,7 @@
         <v>45610</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45140</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59395,7 +59395,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45627</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59541,7 +59541,7 @@
         <v>44658</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>46285</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>46244</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45176</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45273</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46154</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>44874</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60057,7 +60057,7 @@
         <v>46244</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45238</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>44971</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>44708</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>45596</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>46244</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>46244</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>46245</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46245</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>46245</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60802,7 +60802,7 @@
         <v>46245</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>46288</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60948,7 +60948,7 @@
         <v>45617</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>44907</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45229</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>46245</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>46248</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>46293</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61406,7 +61406,7 @@
         <v>46293</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>45273</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61557,7 +61557,7 @@
         <v>45903</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>46247</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>46290</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         <v>46293</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61854,7 +61854,7 @@
         <v>45331</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61927,7 +61927,7 @@
         <v>45741</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62000,7 +62000,7 @@
         <v>45741</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>46247</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62146,7 +62146,7 @@
         <v>46247</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>46247</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45312</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62365,7 +62365,7 @@
         <v>45316</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45056</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62584,7 +62584,7 @@
         <v>45056</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>44813</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62730,7 +62730,7 @@
         <v>45251</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>46251</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62876,7 +62876,7 @@
         <v>46252</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>45254</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>46252</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>46251</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>46294</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>46252</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         <v>45646</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63397,7 +63397,7 @@
         <v>44972</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63470,7 +63470,7 @@
         <v>46294</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63543,7 +63543,7 @@
         <v>46297</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         <v>46297</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63689,7 +63689,7 @@
         <v>45687</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>46297</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>46296</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>46230</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64059,7 +64059,7 @@
         <v>46254</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         <v>44817</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45138</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>46296</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>46254</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>46297</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64507,7 +64507,7 @@
         <v>46297</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64585,7 +64585,7 @@
         <v>46254</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>46254</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>46301</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>45028</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>45177</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>46230</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>46255</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65106,7 +65106,7 @@
         <v>45405</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45434</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45357</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>46258</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>46258</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45782</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>45783</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65705,7 +65705,7 @@
         <v>46301</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>46301</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>45090</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>46230</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46301</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>45462</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>45110</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>46301</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>45315</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>45315</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66450,7 +66450,7 @@
         <v>46301</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66528,7 +66528,7 @@
         <v>45701</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66601,7 +66601,7 @@
         <v>46303</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66674,7 +66674,7 @@
         <v>46303</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66747,7 +66747,7 @@
         <v>45791</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66820,7 +66820,7 @@
         <v>45141</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66893,7 +66893,7 @@
         <v>46260</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66966,7 +66966,7 @@
         <v>44795</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67039,7 +67039,7 @@
         <v>46307</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67117,7 +67117,7 @@
         <v>46262</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67195,7 +67195,7 @@
         <v>45219</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67268,7 +67268,7 @@
         <v>45776</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67341,7 +67341,7 @@
         <v>45313</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67414,7 +67414,7 @@
         <v>45631</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67487,7 +67487,7 @@
         <v>45230</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67560,7 +67560,7 @@
         <v>44538</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67633,7 +67633,7 @@
         <v>46261</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67711,7 +67711,7 @@
         <v>45379</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67784,7 +67784,7 @@
         <v>46262</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67862,7 +67862,7 @@
         <v>45467</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67940,7 +67940,7 @@
         <v>46262</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68013,7 +68013,7 @@
         <v>46309</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68086,7 +68086,7 @@
         <v>46266</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68159,7 +68159,7 @@
         <v>46266</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68232,7 +68232,7 @@
         <v>46266</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>46265</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>45800</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68456,7 +68456,7 @@
         <v>46267</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>46266</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>45347</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68680,7 +68680,7 @@
         <v>46265</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68753,7 +68753,7 @@
         <v>45807</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>45553</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68899,7 +68899,7 @@
         <v>46265</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>46266</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>46309</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69118,7 +69118,7 @@
         <v>45585</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69191,7 +69191,7 @@
         <v>46268</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69269,7 +69269,7 @@
         <v>44531</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69342,7 +69342,7 @@
         <v>46310</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69415,7 +69415,7 @@
         <v>46310</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69488,7 +69488,7 @@
         <v>46310</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>46310</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>46310</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>46268</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69785,7 +69785,7 @@
         <v>45568</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69858,7 +69858,7 @@
         <v>46267</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69936,7 +69936,7 @@
         <v>46268</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70014,7 +70014,7 @@
         <v>46311</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>46268</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70170,7 +70170,7 @@
         <v>46310</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70243,7 +70243,7 @@
         <v>46310</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70316,7 +70316,7 @@
         <v>45820</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70389,7 +70389,7 @@
         <v>45824</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70467,7 +70467,7 @@
         <v>45825</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70545,7 +70545,7 @@
         <v>46268</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>46268</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70691,7 +70691,7 @@
         <v>45827</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70769,7 +70769,7 @@
         <v>46310</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70842,7 +70842,7 @@
         <v>46267</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70920,7 +70920,7 @@
         <v>46311</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>45700</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71071,7 +71071,7 @@
         <v>45832</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71144,7 +71144,7 @@
         <v>45834</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>45848</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71300,7 +71300,7 @@
         <v>45848</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71373,7 +71373,7 @@
         <v>45849</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71451,7 +71451,7 @@
         <v>45799</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71524,7 +71524,7 @@
         <v>45828</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71602,7 +71602,7 @@
         <v>45573</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71675,7 +71675,7 @@
         <v>44596</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71748,7 +71748,7 @@
         <v>44623</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71821,7 +71821,7 @@
         <v>44588</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71894,7 +71894,7 @@
         <v>44879</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71967,7 +71967,7 @@
         <v>44516</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72040,7 +72040,7 @@
         <v>44879</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72113,7 +72113,7 @@
         <v>44775</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72186,7 +72186,7 @@
         <v>44741</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72259,7 +72259,7 @@
         <v>44741</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72332,7 +72332,7 @@
         <v>44687</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72405,7 +72405,7 @@
         <v>44523</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72478,7 +72478,7 @@
         <v>45769</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72551,7 +72551,7 @@
         <v>45544</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72624,7 +72624,7 @@
         <v>45873</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>45442</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72775,7 +72775,7 @@
         <v>45874</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>45874</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72931,7 +72931,7 @@
         <v>45880</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>45880</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73077,7 +73077,7 @@
         <v>45476</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73150,7 +73150,7 @@
         <v>45113</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>45013</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73306,7 +73306,7 @@
         <v>45114</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>45440</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>44825</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -73525,7 +73525,7 @@
         <v>45070</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -73598,7 +73598,7 @@
         <v>44741</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73676,7 +73676,7 @@
         <v>45688</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>45743</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         <v>45743</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>45743</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -73968,7 +73968,7 @@
         <v>45743</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>46127</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74114,7 +74114,7 @@
         <v>46147</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74187,7 +74187,7 @@
         <v>46309</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>46053</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>46167</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>46274</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>46297</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>45799</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>45701</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>46050</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>46262</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45028</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44852</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46170</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45119</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46275</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44553</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44727</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45890</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45925</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45926</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>46274</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>46276</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45491</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45761</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45236</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45334</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45955</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>46045</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>46064</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45202</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45846</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>46217</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46293</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>46248</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>46296</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>46258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46301</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>46258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45789</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44538</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44525</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45439</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45096</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45224</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45564</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45945</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>45971</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45644</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>46164</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>46167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45992</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>46049</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>46055</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45114</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>44525</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46191</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45243</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>46206</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45625</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>46210</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45450</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>46220</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>46225</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>46272</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>46276</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46280</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>46237</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>46283</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>46258</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45491</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46302</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>46262</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>46175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45356</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45820</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45544</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44636</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45768</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>46184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44866</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44536</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44538</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44747</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44498</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>44857</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>44777</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44495</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44816</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>44848</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44599</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44502</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44489</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44816</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44499</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44817</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44496</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44818</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44590</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>44820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44886</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>44590</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>44538</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44571</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45363</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>45478</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45601</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45532</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>44942</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45440</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>44941</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45747</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45363</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45670</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45523</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45511</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45418</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45350</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45350</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45684</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45254</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45425</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44538</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45576</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45180</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44708</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44806</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45208</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45544</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>44911</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45320</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45356</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45467</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>44859</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45309</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45345</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45110</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45376</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45145</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45219</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44792</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45644</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45414</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45215</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44592</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         <v>45090</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45257</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45183</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>44977</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45350</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45262</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45681</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45604</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45574</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45324</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>44890</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45187</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45484</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45323</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45642</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45503</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45559</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45287</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44685</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45574</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45574</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45457</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44615</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45559</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45559</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45188</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>44756</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45230</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45285</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45685</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45618</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45883</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45849</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45377</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45167</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45946</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45664</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45684</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45244</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45862</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45714</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45760</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45831</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>46136</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45827</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44722</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45370</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45894</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45531</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45574</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>44782</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45462</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45769</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45764</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45901</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45936</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45965</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45891</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>45894</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45908</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45894</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45896</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45897</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45642</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45924</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45375</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45664</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45911</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45797</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45678</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45842</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45972</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>46034</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45890</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45934</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45467</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45478</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45958</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45021</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45880</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45905</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45904</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45904</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45924</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45225</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>46140</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45776</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45911</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45915</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45912</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45098</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45912</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45916</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45281</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45922</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45924</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45924</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45924</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45929</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45376</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45929</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45929</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45929</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45926</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45929</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45098</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45237</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>46150</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>46150</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46153</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46150</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45935</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45935</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45935</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45324</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>46150</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44874</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45393</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45376</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45940</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45940</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45334</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45940</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45180</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45944</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45783</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45945</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>44824</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>45945</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44608</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45946</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45552</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45646</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45950</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44917</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45951</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45953</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45345</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45952</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>46154</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45957</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45955</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45956</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45955</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45955</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45952</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>45553</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>45955</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45959</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45419</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>45245</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45960</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45960</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>46161</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45232</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45960</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45271</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45964</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46161</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45573</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45631</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45912</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45971</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45971</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45968</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45642</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>46162</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44525</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46162</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45419</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45975</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45139</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45978</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45987</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45625</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45097</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45881</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45981</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45981</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45981</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45980</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45985</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>45265</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>45985</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45982</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45596</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45982</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45266</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45264</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45955</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45985</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45985</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45239</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45986</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45700</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>45986</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45988</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>46168</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>46168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45993</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>44656</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>44550</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45308</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45478</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45478</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45995</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45742</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45741</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45695</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45993</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45995</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45035</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45035</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45620</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45952</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45188</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45478</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>46002</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45705</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>46002</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45726</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46006</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>46006</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>46006</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>46006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>46006</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46006</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>46006</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>46006</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>46006</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45930</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45129</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45541</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45278</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>46008</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>46008</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45926</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45926</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46010</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46013</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46010</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45926</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46171</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46013</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45618</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45938</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45951</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45986</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45936</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45644</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45936</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45936</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45936</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45936</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45586</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45586</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45558</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45691</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>46177</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>46177</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>46031</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>45951</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>46177</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>46036</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>46036</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>46036</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46177</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>46036</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>46038</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46038</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>46177</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46178</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>46177</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>46043</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>46042</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46042</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>46042</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45434</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>46042</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>46042</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46042</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>46042</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46045</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45605</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>46044</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>46044</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45202</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45772</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>46048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>46048</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>46049</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>46050</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>46051</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>46051</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>44529</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>46057</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>46183</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45215</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45706</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>46058</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45741</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>46183</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>44929</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>44929</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45537</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>45644</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>46183</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>46188</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>46068</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45526</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45601</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45484</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>46080</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>46083</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45015</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45553</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45285</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45243</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>46087</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>45243</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>46087</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>46190</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>44817</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>44817</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45434</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>46092</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45244</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44539</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45582</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45120</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45120</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45578</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45546</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>46197</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>44984</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>46195</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>46197</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45681</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>46036</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50269,7 +50269,7 @@
         <v>45188</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>45419</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>46122</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45545</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46126</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45688</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>45579</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45579</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45579</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45579</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45222</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>44685</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>46203</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45505</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46203</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46135</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46135</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46135</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>46203</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45630</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45937</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45819</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>46205</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45936</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45239</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45904</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45641</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>44942</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45833</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45848</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44813</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45677</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>46206</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>46205</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46210</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>46210</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>45559</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>45593</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>45117</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46212</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46197</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46212</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>46212</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53551,7 +53551,7 @@
         <v>46211</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46212</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>46212</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>44890</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>46206</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45401</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45273</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54072,7 +54072,7 @@
         <v>46217</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54150,7 +54150,7 @@
         <v>46217</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>46191</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45187</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>46111</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45974</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45987</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>45491</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>46191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46223</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>46223</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46223</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>46223</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>46223</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46226</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>46226</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55280,7 +55280,7 @@
         <v>46272</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>46126</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45245</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46230</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>46272</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>46272</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>46273</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>46274</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>45527</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45527</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>46275</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45098</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>45639</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45749</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45239</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45559</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45603</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>46276</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>46237</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>46237</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46280</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>44785</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>46280</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>46237</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>46237</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57384,7 +57384,7 @@
         <v>46230</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>46280</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45211</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57603,7 +57603,7 @@
         <v>46238</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57681,7 +57681,7 @@
         <v>45167</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45090</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45043</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>46237</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>45607</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>46283</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45125</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>45125</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>46281</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>46283</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58426,7 +58426,7 @@
         <v>46275</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>44888</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>45478</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45478</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>44622</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>46275</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>44942</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>46286</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>46286</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45420</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59166,7 +59166,7 @@
         <v>45981</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59239,7 +59239,7 @@
         <v>45610</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45140</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59395,7 +59395,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45627</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59541,7 +59541,7 @@
         <v>44658</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>46285</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>46244</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45176</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45273</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46154</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>44874</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60057,7 +60057,7 @@
         <v>46244</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45238</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>44971</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>44708</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>45596</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>46244</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>46244</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>46245</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46245</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>46245</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60802,7 +60802,7 @@
         <v>46245</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>46288</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60948,7 +60948,7 @@
         <v>45617</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>44907</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45229</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>46245</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>46248</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>46293</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61406,7 +61406,7 @@
         <v>46293</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>45273</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61557,7 +61557,7 @@
         <v>45903</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>46247</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>46290</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         <v>46293</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61854,7 +61854,7 @@
         <v>45331</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61927,7 +61927,7 @@
         <v>45741</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62000,7 +62000,7 @@
         <v>45741</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>46247</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62146,7 +62146,7 @@
         <v>46247</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>46247</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45312</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62365,7 +62365,7 @@
         <v>45316</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45056</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62584,7 +62584,7 @@
         <v>45056</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>44813</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62730,7 +62730,7 @@
         <v>45251</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>46251</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62876,7 +62876,7 @@
         <v>46252</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>45254</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>46252</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>46251</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>46294</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>46252</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         <v>45646</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63397,7 +63397,7 @@
         <v>44972</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63470,7 +63470,7 @@
         <v>46294</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63543,7 +63543,7 @@
         <v>46297</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         <v>46297</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63689,7 +63689,7 @@
         <v>45687</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>46297</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>46296</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>46230</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64059,7 +64059,7 @@
         <v>46254</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         <v>44817</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45138</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>46296</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>46254</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>46297</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64507,7 +64507,7 @@
         <v>46297</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64585,7 +64585,7 @@
         <v>46254</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>46254</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>46301</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>45028</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>45177</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>46230</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>46255</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65106,7 +65106,7 @@
         <v>45405</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45434</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45357</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>46258</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>46258</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45782</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>45783</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65705,7 +65705,7 @@
         <v>46301</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>46301</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>45090</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>46230</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46301</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>45462</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>45110</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>46301</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>45315</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>45315</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66450,7 +66450,7 @@
         <v>46301</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66528,7 +66528,7 @@
         <v>45701</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66601,7 +66601,7 @@
         <v>46303</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66674,7 +66674,7 @@
         <v>46303</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66747,7 +66747,7 @@
         <v>45791</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66820,7 +66820,7 @@
         <v>45141</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66893,7 +66893,7 @@
         <v>46260</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66966,7 +66966,7 @@
         <v>44795</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67039,7 +67039,7 @@
         <v>46307</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67117,7 +67117,7 @@
         <v>46262</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67195,7 +67195,7 @@
         <v>45219</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67268,7 +67268,7 @@
         <v>45776</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67341,7 +67341,7 @@
         <v>45313</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67414,7 +67414,7 @@
         <v>45631</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67487,7 +67487,7 @@
         <v>45230</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67560,7 +67560,7 @@
         <v>44538</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67633,7 +67633,7 @@
         <v>46261</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67711,7 +67711,7 @@
         <v>45379</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67784,7 +67784,7 @@
         <v>46262</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67862,7 +67862,7 @@
         <v>45467</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67940,7 +67940,7 @@
         <v>46262</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68013,7 +68013,7 @@
         <v>46309</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68086,7 +68086,7 @@
         <v>46266</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68159,7 +68159,7 @@
         <v>46266</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68232,7 +68232,7 @@
         <v>46266</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>46265</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>45800</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68456,7 +68456,7 @@
         <v>46267</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>46266</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>45347</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68680,7 +68680,7 @@
         <v>46265</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68753,7 +68753,7 @@
         <v>45807</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>45553</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68899,7 +68899,7 @@
         <v>46265</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>46266</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>46309</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69118,7 +69118,7 @@
         <v>45585</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69191,7 +69191,7 @@
         <v>46268</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69269,7 +69269,7 @@
         <v>44531</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69342,7 +69342,7 @@
         <v>46310</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69415,7 +69415,7 @@
         <v>46310</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69488,7 +69488,7 @@
         <v>46310</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>46310</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>46310</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>46268</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69785,7 +69785,7 @@
         <v>45568</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69858,7 +69858,7 @@
         <v>46267</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -69936,7 +69936,7 @@
         <v>46268</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70014,7 +70014,7 @@
         <v>46311</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>46268</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70170,7 +70170,7 @@
         <v>46310</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70243,7 +70243,7 @@
         <v>46310</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70316,7 +70316,7 @@
         <v>45820</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70389,7 +70389,7 @@
         <v>45824</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70467,7 +70467,7 @@
         <v>45825</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70545,7 +70545,7 @@
         <v>46268</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>46268</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70691,7 +70691,7 @@
         <v>45827</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70769,7 +70769,7 @@
         <v>46310</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70842,7 +70842,7 @@
         <v>46267</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70920,7 +70920,7 @@
         <v>46311</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>45700</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71071,7 +71071,7 @@
         <v>45832</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71144,7 +71144,7 @@
         <v>45834</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>45848</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71300,7 +71300,7 @@
         <v>45848</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71373,7 +71373,7 @@
         <v>45849</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71451,7 +71451,7 @@
         <v>45799</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71524,7 +71524,7 @@
         <v>45828</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71602,7 +71602,7 @@
         <v>45573</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71675,7 +71675,7 @@
         <v>44596</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71748,7 +71748,7 @@
         <v>44623</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71821,7 +71821,7 @@
         <v>44588</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71894,7 +71894,7 @@
         <v>44879</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -71967,7 +71967,7 @@
         <v>44516</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72040,7 +72040,7 @@
         <v>44879</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72113,7 +72113,7 @@
         <v>44775</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72186,7 +72186,7 @@
         <v>44741</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72259,7 +72259,7 @@
         <v>44741</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72332,7 +72332,7 @@
         <v>44687</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72405,7 +72405,7 @@
         <v>44523</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72478,7 +72478,7 @@
         <v>45769</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72551,7 +72551,7 @@
         <v>45544</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72624,7 +72624,7 @@
         <v>45873</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>45442</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72775,7 +72775,7 @@
         <v>45874</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>45874</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -72931,7 +72931,7 @@
         <v>45880</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>45880</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73077,7 +73077,7 @@
         <v>45476</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73150,7 +73150,7 @@
         <v>45113</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>45013</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73306,7 +73306,7 @@
         <v>45114</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>45440</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>44825</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -73525,7 +73525,7 @@
         <v>45070</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -73598,7 +73598,7 @@
         <v>44741</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73676,7 +73676,7 @@
         <v>45688</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>45743</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         <v>45743</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>45743</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -73968,7 +73968,7 @@
         <v>45743</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>46127</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74114,7 +74114,7 @@
         <v>46147</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74187,7 +74187,7 @@
         <v>46309</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46190</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>46053</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>46258</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>45257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>46167</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44539</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>46297</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46262</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45028</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44852</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46170</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45968</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45119</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45446</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45491</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>46282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45926</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>46294</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>45925</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>45890</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>46276</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45243</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44705</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>46184</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>46217</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>46045</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46248</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>46064</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>46296</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45120</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>46301</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45202</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45747</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>46293</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45236</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45789</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44538</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45902</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>46164</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>46167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45945</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46183</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>46191</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45971</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>46206</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>46210</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45992</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45564</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>46220</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46225</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>46008</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46280</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>46283</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46049</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>46055</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45356</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45831</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>46258</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45544</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>46262</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46175</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45565</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>46272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45827</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>46276</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45600</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45243</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45096</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44525</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45114</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45450</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45644</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>44525</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45625</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45224</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45439</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44636</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45768</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46184</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44866</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44536</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44531</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44538</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44747</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44498</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44857</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44495</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44816</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44848</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44599</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44502</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44708</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44816</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>44499</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44817</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44496</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44818</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44590</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44886</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>44590</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>44538</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44571</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45764</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45705</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45883</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45419</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44615</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45769</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45681</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45894</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45891</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45642</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45896</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45604</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45334</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45043</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45316</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45377</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45897</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45257</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45350</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45897</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45176</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45425</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45603</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45904</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45880</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45904</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44819</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45593</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45905</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>46161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45245</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45912</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>46162</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44942</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>46161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44708</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>46162</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45955</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45916</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45363</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44538</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45922</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45400</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45700</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45924</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45211</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>45924</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45926</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45097</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45925</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>46168</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>46168</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45925</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45419</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45929</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45929</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45929</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45356</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45935</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45935</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45254</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45935</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45232</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44817</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45350</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45607</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45940</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45308</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45940</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45940</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45944</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>44888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44813</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46177</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45309</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>46177</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>46177</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>46177</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>46177</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45254</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45239</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45783</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>46177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45945</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>44824</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45478</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45478</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45946</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45537</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45620</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45523</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>46036</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45457</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>46178</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44813</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45951</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46183</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45952</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45953</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46183</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45955</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45955</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45955</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45955</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45956</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45957</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45957</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45960</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45960</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45960</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45960</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45959</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45467</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44984</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45964</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45271</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45264</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45434</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>46188</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45968</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46190</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45418</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>46195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45971</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45222</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>46197</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>46197</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45726</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44708</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45974</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45625</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>44874</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45237</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45579</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45579</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45140</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45331</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46203</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45478</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46203</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45982</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45440</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46203</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45981</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45618</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46205</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45985</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46205</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45986</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45986</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45559</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45985</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45278</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45462</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45573</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46206</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45631</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45988</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45434</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46197</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>46210</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45125</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45125</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45574</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46210</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45989</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45993</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45993</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46212</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>46212</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>46212</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46212</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46212</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45639</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45742</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45741</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45995</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45995</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46217</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45237</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46206</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46191</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46223</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46191</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45952</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46223</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45987</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46002</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>46223</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>46223</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>46111</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46223</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45357</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>46002</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>46006</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45405</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45434</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>46006</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46226</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45782</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45782</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46006</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>46126</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46006</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>46226</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46006</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46006</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46006</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45783</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46006</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46008</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46230</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45749</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46008</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45926</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46237</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>46010</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>46237</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>46237</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46280</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>46010</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>45315</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45315</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>45926</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45926</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45930</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45090</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45110</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>46280</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>46013</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>46237</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>46280</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>46013</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45936</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>45951</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45986</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45938</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45936</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45936</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45936</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45586</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45586</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45701</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45462</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45691</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46238</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>46230</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45141</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45951</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46283</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>46285</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>46154</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45791</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45117</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>44795</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46286</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>46036</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>46036</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45230</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45631</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46036</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>46038</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>46283</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>46281</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46286</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45219</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>46042</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>46042</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>46042</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46042</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>46042</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45313</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46042</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44538</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>46038</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>46245</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>46042</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>46245</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45981</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>46044</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>46044</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>46245</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>46245</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>46244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>46043</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43537,7 +43537,7 @@
         <v>46043</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>46048</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>46288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>46244</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46048</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46244</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>46045</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45467</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46244</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45379</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>46247</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45800</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46049</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46050</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>46051</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45347</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46051</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45553</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>46290</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>46247</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>46247</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45273</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44531</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45807</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>46247</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46057</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>46058</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>44950</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45585</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>46293</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45568</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>46293</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>46294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>46293</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>46068</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>46248</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45820</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45266</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>46252</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>46251</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45824</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45825</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>46252</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>46252</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45827</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>46080</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>46296</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45832</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>46083</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45700</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45035</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>46297</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>46087</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>46087</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>46254</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>45834</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>46255</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>46092</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>46297</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>46230</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45244</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>46254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45505</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>45478</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>46297</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46297</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>46297</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>46254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>46254</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>46230</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>46230</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>46252</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49268,7 +49268,7 @@
         <v>45544</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>46301</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45848</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>46301</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>46301</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>46301</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45848</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45849</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45180</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45488</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>46258</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46258</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>46301</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>46301</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45532</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50408,7 +50408,7 @@
         <v>45532</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45828</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>46036</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45573</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>45799</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>44741</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>44879</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>44879</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>44741</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>44516</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>44523</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>44588</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>44687</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44775</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>44623</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>44596</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45511</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45769</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45544</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>46261</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>45442</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>46260</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46303</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>44539</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45559</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45559</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>45873</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45610</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>46122</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45635</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>45874</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>46126</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45874</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>46303</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>46262</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46307</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>46265</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>45880</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45880</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45776</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>46262</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>44592</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45545</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45618</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46262</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>46135</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>44608</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45644</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46136</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>46135</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45491</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>46310</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>46310</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>46310</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46310</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>46135</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>46310</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>46309</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46265</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46266</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>46266</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>46266</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>44942</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>46310</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>46267</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45842</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>46266</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>45898</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>46310</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>46266</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>46267</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>46310</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>46309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45641</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45741</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45021</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45776</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>45375</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>46311</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>45924</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>46311</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45936</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45323</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>46268</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>46314</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45985</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45831</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45958</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46267</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>45972</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>45664</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>46268</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>45862</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>45120</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57541,7 +57541,7 @@
         <v>46268</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57614,7 +57614,7 @@
         <v>45120</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57687,7 +57687,7 @@
         <v>45578</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>46314</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45946</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45936</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>45760</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>46268</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>45849</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46314</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58281,7 +58281,7 @@
         <v>46034</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>46268</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>46268</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>45015</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45924</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45714</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>46272</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45833</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>45894</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58953,7 +58953,7 @@
         <v>45797</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45908</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59099,7 +59099,7 @@
         <v>45531</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>45848</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>45664</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59323,7 +59323,7 @@
         <v>46316</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>46272</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59474,7 +59474,7 @@
         <v>45370</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59547,7 +59547,7 @@
         <v>46273</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>45901</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59698,7 +59698,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>45819</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>46315</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45484</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45478</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45145</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60136,7 +60136,7 @@
         <v>45965</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>46272</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>46272</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60365,7 +60365,7 @@
         <v>45630</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45904</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>45684</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>45890</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45264</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45937</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>46140</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45942</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60959,7 +60959,7 @@
         <v>45911</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61032,7 +61032,7 @@
         <v>46142</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61105,7 +61105,7 @@
         <v>45244</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61178,7 +61178,7 @@
         <v>45028</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45934</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61402,7 +61402,7 @@
         <v>46275</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45541</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61548,7 +61548,7 @@
         <v>45285</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45419</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61694,7 +61694,7 @@
         <v>46317</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>46317</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>46317</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61923,7 +61923,7 @@
         <v>44622</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61996,7 +61996,7 @@
         <v>46287</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>46276</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
         <v>46317</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62225,7 +62225,7 @@
         <v>46317</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62298,7 +62298,7 @@
         <v>45548</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>44977</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>46150</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>46150</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>46150</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62668,7 +62668,7 @@
         <v>46150</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62741,7 +62741,7 @@
         <v>46153</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62814,7 +62814,7 @@
         <v>44782</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>46154</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62960,7 +62960,7 @@
         <v>45553</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63033,7 +63033,7 @@
         <v>45741</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63106,7 +63106,7 @@
         <v>45741</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>44941</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63252,7 +63252,7 @@
         <v>45912</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63325,7 +63325,7 @@
         <v>45175</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>44756</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45574</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45098</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63622,7 +63622,7 @@
         <v>45323</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63695,7 +63695,7 @@
         <v>44817</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63773,7 +63773,7 @@
         <v>44722</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>45644</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>45642</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>45642</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
         <v>44929</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>44929</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>44911</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>44907</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45695</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>45553</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>45681</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>44859</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64659,7 +64659,7 @@
         <v>45183</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45098</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>44890</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>45188</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>45677</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65044,7 +65044,7 @@
         <v>45685</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65117,7 +65117,7 @@
         <v>45478</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65190,7 +65190,7 @@
         <v>44895</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>45670</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45526</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>45239</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45688</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65570,7 +65570,7 @@
         <v>45265</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65643,7 +65643,7 @@
         <v>45523</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65716,7 +65716,7 @@
         <v>45180</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>45772</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65867,7 +65867,7 @@
         <v>45262</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>45345</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>44972</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45167</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66164,7 +66164,7 @@
         <v>45225</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66237,7 +66237,7 @@
         <v>45558</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66315,7 +66315,7 @@
         <v>45376</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66388,7 +66388,7 @@
         <v>44890</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>45090</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66534,7 +66534,7 @@
         <v>45285</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66607,7 +66607,7 @@
         <v>45312</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66680,7 +66680,7 @@
         <v>45110</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66753,7 +66753,7 @@
         <v>45188</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66831,7 +66831,7 @@
         <v>45350</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66904,7 +66904,7 @@
         <v>45582</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66982,7 +66982,7 @@
         <v>45245</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67055,7 +67055,7 @@
         <v>44685</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67128,7 +67128,7 @@
         <v>44550</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67201,7 +67201,7 @@
         <v>45363</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67279,7 +67279,7 @@
         <v>45376</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67352,7 +67352,7 @@
         <v>45574</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67430,7 +67430,7 @@
         <v>45574</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45139</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67581,7 +67581,7 @@
         <v>45247</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67654,7 +67654,7 @@
         <v>45229</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67732,7 +67732,7 @@
         <v>45467</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67805,7 +67805,7 @@
         <v>44529</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45376</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67951,7 +67951,7 @@
         <v>45324</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68029,7 +68029,7 @@
         <v>45627</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68102,7 +68102,7 @@
         <v>45202</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68180,7 +68180,7 @@
         <v>45273</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68253,7 +68253,7 @@
         <v>45747</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68326,7 +68326,7 @@
         <v>45239</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68399,7 +68399,7 @@
         <v>45503</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68472,7 +68472,7 @@
         <v>45401</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68545,7 +68545,7 @@
         <v>45527</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68623,7 +68623,7 @@
         <v>45527</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>45576</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68774,7 +68774,7 @@
         <v>44806</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68847,7 +68847,7 @@
         <v>45420</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68920,7 +68920,7 @@
         <v>45559</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68993,7 +68993,7 @@
         <v>45596</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>45478</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>45208</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69217,7 +69217,7 @@
         <v>45187</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>45644</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69363,7 +69363,7 @@
         <v>45230</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69436,7 +69436,7 @@
         <v>45601</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69509,7 +69509,7 @@
         <v>45056</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69582,7 +69582,7 @@
         <v>45056</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45043</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69733,7 +69733,7 @@
         <v>45605</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69806,7 +69806,7 @@
         <v>45345</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69879,7 +69879,7 @@
         <v>45684</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69952,7 +69952,7 @@
         <v>44658</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70025,7 +70025,7 @@
         <v>45097</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>44685</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70176,7 +70176,7 @@
         <v>45090</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70249,7 +70249,7 @@
         <v>45687</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>45600</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70400,7 +70400,7 @@
         <v>45188</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70478,7 +70478,7 @@
         <v>45239</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70551,7 +70551,7 @@
         <v>45706</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70629,7 +70629,7 @@
         <v>45238</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45138</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70775,7 +70775,7 @@
         <v>44656</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70848,7 +70848,7 @@
         <v>45642</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70921,7 +70921,7 @@
         <v>45098</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70999,7 +70999,7 @@
         <v>45243</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71077,7 +71077,7 @@
         <v>45243</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71155,7 +71155,7 @@
         <v>45177</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71228,7 +71228,7 @@
         <v>44683</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71301,7 +71301,7 @@
         <v>45215</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>44792</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71447,7 +71447,7 @@
         <v>45129</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71520,7 +71520,7 @@
         <v>45414</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71593,7 +71593,7 @@
         <v>45215</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>45244</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>45245</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71812,7 +71812,7 @@
         <v>45167</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71890,7 +71890,7 @@
         <v>45320</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71963,7 +71963,7 @@
         <v>45219</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72036,7 +72036,7 @@
         <v>45251</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72109,7 +72109,7 @@
         <v>45287</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72182,7 +72182,7 @@
         <v>45265</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72255,7 +72255,7 @@
         <v>44785</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72328,7 +72328,7 @@
         <v>45484</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72406,7 +72406,7 @@
         <v>45324</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72484,7 +72484,7 @@
         <v>44685</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72557,7 +72557,7 @@
         <v>45187</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72630,7 +72630,7 @@
         <v>45273</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72703,7 +72703,7 @@
         <v>45393</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72776,7 +72776,7 @@
         <v>44874</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72854,7 +72854,7 @@
         <v>44984</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72927,7 +72927,7 @@
         <v>45579</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73000,7 +73000,7 @@
         <v>45579</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73073,7 +73073,7 @@
         <v>45601</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73146,7 +73146,7 @@
         <v>44971</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73219,7 +73219,7 @@
         <v>45552</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73292,7 +73292,7 @@
         <v>45646</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73365,7 +73365,7 @@
         <v>45678</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -73438,7 +73438,7 @@
         <v>45646</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -73511,7 +73511,7 @@
         <v>45559</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -73584,7 +73584,7 @@
         <v>44525</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -73657,7 +73657,7 @@
         <v>45546</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73735,7 +73735,7 @@
         <v>45476</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73808,7 +73808,7 @@
         <v>45113</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73886,7 +73886,7 @@
         <v>45013</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73964,7 +73964,7 @@
         <v>45114</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74037,7 +74037,7 @@
         <v>45440</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74110,7 +74110,7 @@
         <v>44825</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74183,7 +74183,7 @@
         <v>45070</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74256,7 +74256,7 @@
         <v>44741</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -74334,7 +74334,7 @@
         <v>45688</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -74407,7 +74407,7 @@
         <v>45743</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -74480,7 +74480,7 @@
         <v>45743</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -74553,7 +74553,7 @@
         <v>45743</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -74626,7 +74626,7 @@
         <v>45743</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46127</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -74772,7 +74772,7 @@
         <v>46147</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -74845,7 +74845,7 @@
         <v>46309</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>46190</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>46053</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>46258</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>45257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>46167</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44539</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>46297</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46262</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45028</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44852</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45260</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46170</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45968</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46275</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45119</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45446</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45491</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>46282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45926</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>46294</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>45925</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>45890</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>46276</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45243</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44705</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45923</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>46184</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>46217</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>46045</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46248</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>46064</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>46296</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45120</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>46301</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45202</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45747</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>46293</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45236</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45789</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44538</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45902</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>46164</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>46167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45945</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46183</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>46191</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45971</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>46206</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>46210</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45992</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45564</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>46220</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46225</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>46008</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46280</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>46283</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46049</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>46055</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45356</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45831</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>46258</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45544</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>46262</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46175</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45565</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>46272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45827</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>46276</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45600</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45243</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45096</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44525</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45114</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45450</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45644</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>44525</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45625</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45224</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45439</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44636</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45768</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46184</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44866</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44536</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44531</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44538</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44747</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44498</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44857</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44495</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44816</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44848</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44599</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44502</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44708</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44816</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>44499</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44817</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44496</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44818</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44590</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44886</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>44590</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>44538</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44571</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45764</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45705</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45883</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45419</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44615</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45769</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45681</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45894</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45891</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45642</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45896</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45604</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45334</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45043</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45316</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45377</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45897</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45257</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45350</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45897</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45176</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45425</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45603</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45904</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45880</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45904</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44819</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45593</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45905</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>46161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45245</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45912</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>46162</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44942</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>46161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44708</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>46162</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45955</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45916</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45363</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44538</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45922</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45400</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45700</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45924</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45211</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>45924</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45926</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45097</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45925</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>46168</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>46168</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45925</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45419</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45929</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45929</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45929</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45356</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45935</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45935</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45254</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45935</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45232</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44817</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45350</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45607</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45940</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45308</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45940</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45940</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45944</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>44888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44813</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46177</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45309</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>46177</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>46177</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>46177</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>46177</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45254</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45239</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45783</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>46177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45945</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>44824</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45478</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45478</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45946</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45537</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45620</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45523</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>46036</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45457</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>46178</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44813</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45951</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46183</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45952</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45953</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46183</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45955</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45955</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45955</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45955</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45956</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45957</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45957</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45960</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45960</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45960</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45960</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45959</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45467</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44984</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45964</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45271</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45264</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45434</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>46188</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45968</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46190</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45418</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>46195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45971</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45222</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>46197</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>46197</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45726</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44708</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45974</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45625</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>44874</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45237</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45579</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45579</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45140</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45331</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46203</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45478</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46203</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45982</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45440</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46203</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45981</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45618</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46205</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45985</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46205</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45986</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45986</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45559</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45985</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45278</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45462</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45573</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46206</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45631</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45988</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45434</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46197</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>46210</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45125</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45125</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45574</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46210</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45989</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45993</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45993</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46212</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>46212</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>46212</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46212</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46212</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45639</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45742</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45741</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45995</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45995</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46217</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45237</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46206</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46191</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46223</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46191</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45952</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46223</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45987</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46002</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>46223</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>46223</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>46111</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46223</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45357</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>46002</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>46006</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45405</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45434</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>46006</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46226</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45782</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45782</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46006</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>46126</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46006</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>46226</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46006</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46006</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46006</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45783</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46006</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46008</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46230</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45749</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46008</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45926</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46237</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>46010</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>46237</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>46237</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46280</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>46010</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>45315</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45315</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>45926</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45926</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45930</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45090</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45110</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>46280</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>46013</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>46237</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>46280</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>46013</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45936</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>45951</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45986</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45938</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45936</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45936</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45936</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45586</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45586</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45701</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45462</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45691</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46238</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>46230</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45141</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45951</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46283</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>46285</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>46154</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45791</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45117</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>44795</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46286</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>46036</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>46036</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45230</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45631</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46036</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>46038</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>46283</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>46281</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46286</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45219</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>46042</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>46042</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>46042</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46042</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>46042</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45313</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46042</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44538</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>46038</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>46245</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>46042</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>46245</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45981</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>46044</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>46044</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>46245</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>46245</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>46244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>46043</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43537,7 +43537,7 @@
         <v>46043</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>46048</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>46288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>46244</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46048</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46244</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>46045</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45467</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46244</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45379</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>46247</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45800</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46049</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46050</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>46051</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45347</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46051</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45553</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>46290</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>46247</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>46247</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45273</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44531</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45807</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>46247</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46057</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>46058</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>44950</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45585</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>46293</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45568</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>46293</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>46294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>46293</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>46068</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>46248</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45820</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45266</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>46252</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>46251</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45824</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45825</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>46252</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>46252</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45827</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>46080</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>46296</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45832</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>46083</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45700</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45035</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>46297</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>46087</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>46087</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>46254</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>45834</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>46255</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>46092</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>46297</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>46230</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45244</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>46254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45505</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>45478</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>46297</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46297</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>46297</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>46254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>46254</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>46230</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>46230</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>46252</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49268,7 +49268,7 @@
         <v>45544</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>46301</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45848</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>46301</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>46301</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>46301</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45848</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45849</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45180</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45488</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>46258</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46258</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>46301</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>46301</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45532</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50408,7 +50408,7 @@
         <v>45532</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45828</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>46036</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45573</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>45799</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>44741</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>44879</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>44879</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>44741</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>44516</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>44523</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>44588</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>44687</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44775</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>44623</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>44596</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45511</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45769</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45544</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>46261</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>45442</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>46260</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46303</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>44539</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45559</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45559</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>45873</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45610</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>46122</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45635</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>45874</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>46126</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45874</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>46303</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>46262</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46307</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>46265</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>45880</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45880</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45776</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>46262</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>44592</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45545</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45618</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46262</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>46135</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>44608</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45644</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46136</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>46135</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45491</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>46310</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>46310</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>46310</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46310</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>46135</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>46310</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>46309</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46265</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46266</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>46266</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>46266</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>44942</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>46310</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>46267</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45842</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>46266</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>45898</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>46310</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>46266</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>46267</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>46310</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>46309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45641</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45741</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45021</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45776</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>45375</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>46311</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>45924</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>46311</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45936</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45323</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>46268</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>46314</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45985</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45831</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45958</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46267</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>45972</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>45664</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>46268</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>45862</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>45120</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57541,7 +57541,7 @@
         <v>46268</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57614,7 +57614,7 @@
         <v>45120</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57687,7 +57687,7 @@
         <v>45578</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>46314</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45946</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45936</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>45760</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>46268</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>45849</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46314</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58281,7 +58281,7 @@
         <v>46034</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>46268</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>46268</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>45015</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45924</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45714</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>46272</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45833</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>45894</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58953,7 +58953,7 @@
         <v>45797</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45908</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59099,7 +59099,7 @@
         <v>45531</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>45848</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>45664</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59323,7 +59323,7 @@
         <v>46316</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>46272</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59474,7 +59474,7 @@
         <v>45370</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59547,7 +59547,7 @@
         <v>46273</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>45901</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59698,7 +59698,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>45819</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>46315</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45484</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45478</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45145</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60136,7 +60136,7 @@
         <v>45965</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>46272</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>46272</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60365,7 +60365,7 @@
         <v>45630</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45904</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>45684</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>45890</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45264</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45937</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>46140</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45942</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60959,7 +60959,7 @@
         <v>45911</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61032,7 +61032,7 @@
         <v>46142</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61105,7 +61105,7 @@
         <v>45244</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61178,7 +61178,7 @@
         <v>45028</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45934</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61402,7 +61402,7 @@
         <v>46275</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45541</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61548,7 +61548,7 @@
         <v>45285</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45419</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61694,7 +61694,7 @@
         <v>46317</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>46317</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>46317</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61923,7 +61923,7 @@
         <v>44622</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61996,7 +61996,7 @@
         <v>46287</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>46276</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
         <v>46317</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62225,7 +62225,7 @@
         <v>46317</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62298,7 +62298,7 @@
         <v>45548</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>44977</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>46150</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>46150</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>46150</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62668,7 +62668,7 @@
         <v>46150</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62741,7 +62741,7 @@
         <v>46153</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62814,7 +62814,7 @@
         <v>44782</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>46154</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62960,7 +62960,7 @@
         <v>45553</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63033,7 +63033,7 @@
         <v>45741</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63106,7 +63106,7 @@
         <v>45741</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>44941</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63252,7 +63252,7 @@
         <v>45912</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63325,7 +63325,7 @@
         <v>45175</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>44756</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45574</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45098</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63622,7 +63622,7 @@
         <v>45323</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63695,7 +63695,7 @@
         <v>44817</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63773,7 +63773,7 @@
         <v>44722</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>45644</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>45642</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>45642</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
         <v>44929</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>44929</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>44911</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>44907</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45695</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>45553</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>45681</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>44859</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64659,7 +64659,7 @@
         <v>45183</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45098</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>44890</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>45188</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>45677</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65044,7 +65044,7 @@
         <v>45685</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65117,7 +65117,7 @@
         <v>45478</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65190,7 +65190,7 @@
         <v>44895</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>45670</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45526</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>45239</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45688</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65570,7 +65570,7 @@
         <v>45265</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65643,7 +65643,7 @@
         <v>45523</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65716,7 +65716,7 @@
         <v>45180</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>45772</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65867,7 +65867,7 @@
         <v>45262</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>45345</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>44972</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45167</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66164,7 +66164,7 @@
         <v>45225</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66237,7 +66237,7 @@
         <v>45558</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66315,7 +66315,7 @@
         <v>45376</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66388,7 +66388,7 @@
         <v>44890</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>45090</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66534,7 +66534,7 @@
         <v>45285</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66607,7 +66607,7 @@
         <v>45312</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66680,7 +66680,7 @@
         <v>45110</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66753,7 +66753,7 @@
         <v>45188</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66831,7 +66831,7 @@
         <v>45350</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66904,7 +66904,7 @@
         <v>45582</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66982,7 +66982,7 @@
         <v>45245</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67055,7 +67055,7 @@
         <v>44685</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67128,7 +67128,7 @@
         <v>44550</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67201,7 +67201,7 @@
         <v>45363</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67279,7 +67279,7 @@
         <v>45376</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67352,7 +67352,7 @@
         <v>45574</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67430,7 +67430,7 @@
         <v>45574</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45139</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67581,7 +67581,7 @@
         <v>45247</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67654,7 +67654,7 @@
         <v>45229</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67732,7 +67732,7 @@
         <v>45467</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67805,7 +67805,7 @@
         <v>44529</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45376</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67951,7 +67951,7 @@
         <v>45324</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68029,7 +68029,7 @@
         <v>45627</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68102,7 +68102,7 @@
         <v>45202</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68180,7 +68180,7 @@
         <v>45273</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68253,7 +68253,7 @@
         <v>45747</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68326,7 +68326,7 @@
         <v>45239</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68399,7 +68399,7 @@
         <v>45503</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68472,7 +68472,7 @@
         <v>45401</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68545,7 +68545,7 @@
         <v>45527</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68623,7 +68623,7 @@
         <v>45527</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>45576</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68774,7 +68774,7 @@
         <v>44806</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68847,7 +68847,7 @@
         <v>45420</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68920,7 +68920,7 @@
         <v>45559</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68993,7 +68993,7 @@
         <v>45596</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>45478</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>45208</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69217,7 +69217,7 @@
         <v>45187</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>45644</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69363,7 +69363,7 @@
         <v>45230</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69436,7 +69436,7 @@
         <v>45601</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69509,7 +69509,7 @@
         <v>45056</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69582,7 +69582,7 @@
         <v>45056</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45043</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69733,7 +69733,7 @@
         <v>45605</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69806,7 +69806,7 @@
         <v>45345</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69879,7 +69879,7 @@
         <v>45684</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -69952,7 +69952,7 @@
         <v>44658</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70025,7 +70025,7 @@
         <v>45097</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>44685</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70176,7 +70176,7 @@
         <v>45090</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70249,7 +70249,7 @@
         <v>45687</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>45600</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70400,7 +70400,7 @@
         <v>45188</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70478,7 +70478,7 @@
         <v>45239</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70551,7 +70551,7 @@
         <v>45706</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70629,7 +70629,7 @@
         <v>45238</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45138</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -70775,7 +70775,7 @@
         <v>44656</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -70848,7 +70848,7 @@
         <v>45642</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -70921,7 +70921,7 @@
         <v>45098</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -70999,7 +70999,7 @@
         <v>45243</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -71077,7 +71077,7 @@
         <v>45243</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -71155,7 +71155,7 @@
         <v>45177</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -71228,7 +71228,7 @@
         <v>44683</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -71301,7 +71301,7 @@
         <v>45215</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>44792</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -71447,7 +71447,7 @@
         <v>45129</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -71520,7 +71520,7 @@
         <v>45414</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -71593,7 +71593,7 @@
         <v>45215</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>45244</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>45245</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -71812,7 +71812,7 @@
         <v>45167</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -71890,7 +71890,7 @@
         <v>45320</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -71963,7 +71963,7 @@
         <v>45219</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -72036,7 +72036,7 @@
         <v>45251</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -72109,7 +72109,7 @@
         <v>45287</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -72182,7 +72182,7 @@
         <v>45265</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -72255,7 +72255,7 @@
         <v>44785</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -72328,7 +72328,7 @@
         <v>45484</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -72406,7 +72406,7 @@
         <v>45324</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -72484,7 +72484,7 @@
         <v>44685</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -72557,7 +72557,7 @@
         <v>45187</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -72630,7 +72630,7 @@
         <v>45273</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -72703,7 +72703,7 @@
         <v>45393</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -72776,7 +72776,7 @@
         <v>44874</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -72854,7 +72854,7 @@
         <v>44984</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -72927,7 +72927,7 @@
         <v>45579</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -73000,7 +73000,7 @@
         <v>45579</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -73073,7 +73073,7 @@
         <v>45601</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -73146,7 +73146,7 @@
         <v>44971</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -73219,7 +73219,7 @@
         <v>45552</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -73292,7 +73292,7 @@
         <v>45646</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -73365,7 +73365,7 @@
         <v>45678</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -73438,7 +73438,7 @@
         <v>45646</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -73511,7 +73511,7 @@
         <v>45559</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -73584,7 +73584,7 @@
         <v>44525</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -73657,7 +73657,7 @@
         <v>45546</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -73735,7 +73735,7 @@
         <v>45476</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -73808,7 +73808,7 @@
         <v>45113</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -73886,7 +73886,7 @@
         <v>45013</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -73964,7 +73964,7 @@
         <v>45114</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -74037,7 +74037,7 @@
         <v>45440</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -74110,7 +74110,7 @@
         <v>44825</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -74183,7 +74183,7 @@
         <v>45070</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -74256,7 +74256,7 @@
         <v>44741</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -74334,7 +74334,7 @@
         <v>45688</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -74407,7 +74407,7 @@
         <v>45743</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -74480,7 +74480,7 @@
         <v>45743</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -74553,7 +74553,7 @@
         <v>45743</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -74626,7 +74626,7 @@
         <v>45743</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -74699,7 +74699,7 @@
         <v>46127</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -74772,7 +74772,7 @@
         <v>46147</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -74845,7 +74845,7 @@
         <v>46309</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
